--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbrac\OneDrive\Documentos\Nutrição\Produtos\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B584C1-CD9A-49FC-82CC-69D631CAD633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471646C9-E569-42D2-B7CB-331785D43CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{3BD6BFFB-CC8B-41FE-8C98-25F5632F7E13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{3BD6BFFB-CC8B-41FE-8C98-25F5632F7E13}"/>
   </bookViews>
   <sheets>
     <sheet name="food_data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="237">
   <si>
     <t>food_group</t>
   </si>
@@ -1121,3042 +1121,2862 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF1BAE8-3DB4-469E-B8F4-26503F66E798}">
-  <dimension ref="A1:P134"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O1" t="s">
-        <v>156</v>
-      </c>
-      <c r="P1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2">
+        <v>68026</v>
+      </c>
       <c r="D2">
-        <v>68026</v>
+        <v>1245</v>
       </c>
       <c r="E2">
-        <v>1245</v>
+        <v>452.50899863661198</v>
       </c>
       <c r="F2">
-        <v>452.50899863661198</v>
+        <v>4.5</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>1467.293823</v>
       </c>
       <c r="H2">
-        <v>1467.293823</v>
+        <v>0.50016700000000003</v>
       </c>
       <c r="I2">
-        <v>0.50016700000000003</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J2">
-        <v>0.16700000000000001</v>
+        <v>79.070329999999998</v>
       </c>
       <c r="K2">
-        <v>79.070329999999998</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.6830000000000001</v>
       </c>
       <c r="M2">
-        <v>1.6830000000000001</v>
+        <v>7.0434739999999998</v>
       </c>
       <c r="N2">
-        <v>7.0434739999999998</v>
+        <v>1.1226670000000001</v>
       </c>
       <c r="O2">
-        <v>1.1226670000000001</v>
-      </c>
-      <c r="P2">
         <v>0.25725700000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
+      <c r="C3">
+        <v>66017</v>
+      </c>
       <c r="D3">
-        <v>66017</v>
+        <v>330</v>
       </c>
       <c r="E3">
-        <v>330</v>
+        <v>7404.1882297760048</v>
       </c>
       <c r="F3">
-        <v>7404.1882297760048</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>47</v>
+        <v>1463.928711</v>
       </c>
       <c r="H3">
-        <v>1463.928711</v>
+        <v>1.9524170000000001</v>
       </c>
       <c r="I3">
-        <v>1.9524170000000001</v>
+        <v>0.31408999999999998</v>
       </c>
       <c r="J3">
-        <v>0.31408999999999998</v>
+        <v>76.361919999999998</v>
       </c>
       <c r="K3">
-        <v>76.361919999999998</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>3.8995829999999998</v>
       </c>
       <c r="M3">
-        <v>3.8995829999999998</v>
+        <v>7.566643</v>
       </c>
       <c r="N3">
-        <v>7.566643</v>
+        <v>0.87522200000000006</v>
       </c>
       <c r="O3">
-        <v>0.87522200000000006</v>
-      </c>
-      <c r="P3">
         <v>0.40272999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
+      <c r="C4">
+        <v>82021</v>
+      </c>
       <c r="D4">
-        <v>82021</v>
+        <v>330</v>
       </c>
       <c r="E4">
-        <v>330</v>
+        <v>7404.1882297760048</v>
       </c>
       <c r="F4">
-        <v>7404.1882297760048</v>
+        <v>47</v>
       </c>
       <c r="G4">
-        <v>47</v>
+        <v>584.74163820000001</v>
       </c>
       <c r="H4">
-        <v>584.74163820000001</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="I4">
-        <v>0.60899999999999999</v>
+        <v>9.7439999999999999E-2</v>
       </c>
       <c r="J4">
-        <v>9.7439999999999999E-2</v>
+        <v>28.55575</v>
       </c>
       <c r="K4">
-        <v>28.55575</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3.9180000000000001</v>
       </c>
       <c r="M4">
-        <v>3.9180000000000001</v>
+        <v>6.5895830000000002</v>
       </c>
       <c r="N4">
-        <v>6.5895830000000002</v>
+        <v>1.115667</v>
       </c>
       <c r="O4">
-        <v>1.115667</v>
-      </c>
-      <c r="P4">
         <v>0.38264799999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
+      <c r="C5">
+        <v>68002</v>
+      </c>
       <c r="D5">
-        <v>68002</v>
+        <v>5295</v>
       </c>
       <c r="E5">
-        <v>5295</v>
+        <v>503.31988193593691</v>
       </c>
       <c r="F5">
-        <v>503.31988193593691</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>2440.6647950000001</v>
       </c>
       <c r="H5">
-        <v>2440.6647950000001</v>
+        <v>46.314999999999998</v>
       </c>
       <c r="I5">
-        <v>46.314999999999998</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J5">
-        <v>8.6999999999999993</v>
+        <v>20.671769999999999</v>
       </c>
       <c r="K5">
-        <v>20.671769999999999</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6.218</v>
       </c>
       <c r="M5">
-        <v>6.218</v>
+        <v>25.385400000000001</v>
       </c>
       <c r="N5">
-        <v>25.385400000000001</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
         <v>1.183103</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
+      <c r="C6">
+        <v>69024</v>
+      </c>
       <c r="D6">
-        <v>69024</v>
+        <v>3320.9089509884666</v>
       </c>
       <c r="E6">
-        <v>3320.9089509884666</v>
+        <v>4474.4591510944665</v>
       </c>
       <c r="F6">
-        <v>4474.4591510944665</v>
+        <v>26.5</v>
       </c>
       <c r="G6">
-        <v>26.5</v>
+        <v>1299</v>
       </c>
       <c r="H6">
-        <v>1299</v>
+        <v>1.36</v>
       </c>
       <c r="I6">
-        <v>1.36</v>
+        <v>0.21</v>
       </c>
       <c r="J6">
-        <v>0.21</v>
+        <v>59.15</v>
       </c>
       <c r="K6">
-        <v>59.15</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="M6">
-        <v>20.8</v>
+        <v>25.3</v>
       </c>
       <c r="N6">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="O6">
-        <v>25</v>
-      </c>
-      <c r="P6">
         <v>0.39764500000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
+      <c r="C7">
+        <v>68018</v>
+      </c>
       <c r="D7">
-        <v>68018</v>
+        <v>477.7</v>
       </c>
       <c r="E7">
-        <v>477.7</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F7">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G7">
-        <v>57.5</v>
+        <v>1190.630005</v>
       </c>
       <c r="H7">
-        <v>1190.630005</v>
+        <v>1.17</v>
       </c>
       <c r="I7">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="J7">
-        <v>0.4</v>
+        <v>62.929160000000003</v>
       </c>
       <c r="K7">
-        <v>62.929160000000003</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>24.00667</v>
       </c>
       <c r="M7">
-        <v>24.00667</v>
+        <v>17.27083</v>
       </c>
       <c r="N7">
-        <v>17.27083</v>
+        <v>13.65033</v>
       </c>
       <c r="O7">
-        <v>13.65033</v>
-      </c>
-      <c r="P7">
         <v>0.34309299999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
+      <c r="C8">
+        <v>68020</v>
+      </c>
       <c r="D8">
-        <v>68020</v>
+        <v>6272.2906885759003</v>
       </c>
       <c r="E8">
-        <v>6272.2906885759003</v>
+        <v>4954.3609397891696</v>
       </c>
       <c r="F8">
-        <v>4954.3609397891696</v>
+        <v>45.35</v>
       </c>
       <c r="G8">
-        <v>45.35</v>
+        <v>1772.4499510000001</v>
       </c>
       <c r="H8">
-        <v>1772.4499510000001</v>
+        <v>20.6</v>
       </c>
       <c r="I8">
-        <v>20.6</v>
+        <v>3.2259929999999999</v>
       </c>
       <c r="J8">
-        <v>3.2259929999999999</v>
+        <v>57.45</v>
       </c>
       <c r="K8">
-        <v>57.45</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="N8">
-        <v>7.8</v>
+        <v>608.21360000000004</v>
       </c>
       <c r="O8">
-        <v>608.21360000000004</v>
-      </c>
-      <c r="P8">
         <v>1.621861</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
+      <c r="C9">
+        <v>68093</v>
+      </c>
       <c r="D9">
-        <v>68093</v>
+        <v>1408</v>
       </c>
       <c r="E9">
-        <v>1408</v>
+        <v>1243.734377543522</v>
       </c>
       <c r="F9">
-        <v>1243.734377543522</v>
+        <v>8.4665445665445667</v>
       </c>
       <c r="G9">
-        <v>8.4665445665445667</v>
+        <v>367.5849915</v>
       </c>
       <c r="H9">
-        <v>367.5849915</v>
+        <v>0.115</v>
       </c>
       <c r="I9">
-        <v>0.115</v>
+        <v>3.0393E-2</v>
       </c>
       <c r="J9">
-        <v>3.0393E-2</v>
+        <v>21.571449999999999</v>
       </c>
       <c r="K9">
-        <v>21.571449999999999</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.931667</v>
       </c>
       <c r="M9">
-        <v>1.931667</v>
+        <v>0.82355100000000003</v>
       </c>
       <c r="N9">
-        <v>0.82355100000000003</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
         <v>0.64490099999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" t="s">
         <v>13</v>
       </c>
+      <c r="C10">
+        <v>68030</v>
+      </c>
       <c r="D10">
-        <v>68030</v>
+        <v>1266.4734051596067</v>
       </c>
       <c r="E10">
-        <v>1266.4734051596067</v>
+        <v>1320.9335943858805</v>
       </c>
       <c r="F10">
-        <v>1320.9335943858805</v>
+        <v>8.4665445665445667</v>
       </c>
       <c r="G10">
-        <v>8.4665445665445667</v>
+        <v>560.05999759999997</v>
       </c>
       <c r="H10">
-        <v>560.05999759999997</v>
+        <v>0.22</v>
       </c>
       <c r="I10">
-        <v>0.22</v>
+        <v>4.5467E-2</v>
       </c>
       <c r="J10">
-        <v>4.5467E-2</v>
+        <v>32.589860000000002</v>
       </c>
       <c r="K10">
-        <v>32.589860000000002</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2.085556</v>
       </c>
       <c r="M10">
-        <v>2.085556</v>
+        <v>0.98014500000000004</v>
       </c>
       <c r="N10">
-        <v>0.98014500000000004</v>
+        <v>1.9510339999999999</v>
       </c>
       <c r="O10">
-        <v>1.9510339999999999</v>
-      </c>
-      <c r="P10">
         <v>0.29755399999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
+      <c r="C11">
+        <v>68031</v>
+      </c>
       <c r="D11">
-        <v>68031</v>
+        <v>1106</v>
       </c>
       <c r="E11">
-        <v>1106</v>
+        <v>1203.6139137517953</v>
       </c>
       <c r="F11">
-        <v>1203.6139137517953</v>
+        <v>8.4665445665445667</v>
       </c>
       <c r="G11">
-        <v>8.4665445665445667</v>
+        <v>305.28399660000002</v>
       </c>
       <c r="H11">
-        <v>305.28399660000002</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="I11">
-        <v>3.7999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="J11">
-        <v>0.01</v>
+        <v>16.53565</v>
       </c>
       <c r="K11">
-        <v>16.53565</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M11">
-        <v>1.32</v>
+        <v>2.038348</v>
       </c>
       <c r="N11">
-        <v>2.038348</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
         <v>0.25440499999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" t="s">
         <v>15</v>
       </c>
+      <c r="C12">
+        <v>68032</v>
+      </c>
       <c r="D12">
-        <v>68032</v>
+        <v>893.33333333333337</v>
       </c>
       <c r="E12">
-        <v>893.33333333333337</v>
+        <v>3854.9260620389368</v>
       </c>
       <c r="F12">
-        <v>3854.9260620389368</v>
+        <v>57.5</v>
       </c>
       <c r="G12">
-        <v>57.5</v>
+        <v>194.93333440000001</v>
       </c>
       <c r="H12">
-        <v>194.93333440000001</v>
+        <v>0.09</v>
       </c>
       <c r="I12">
-        <v>0.09</v>
+        <v>1.4E-2</v>
       </c>
       <c r="J12">
-        <v>1.4E-2</v>
+        <v>11.11101</v>
       </c>
       <c r="K12">
-        <v>11.11101</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3.3733330000000001</v>
       </c>
       <c r="M12">
-        <v>3.3733330000000001</v>
+        <v>1.9456519999999999</v>
       </c>
       <c r="N12">
-        <v>1.9456519999999999</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="O12">
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="P12">
         <v>0.30496899999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" t="s">
         <v>16</v>
       </c>
+      <c r="C13">
+        <v>68034</v>
+      </c>
       <c r="D13">
-        <v>68034</v>
+        <v>794.44444444444446</v>
       </c>
       <c r="E13">
-        <v>794.44444444444446</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F13">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G13">
-        <v>57.5</v>
+        <v>128.39166259999999</v>
       </c>
       <c r="H13">
-        <v>128.39166259999999</v>
+        <v>0.21266699999999999</v>
       </c>
       <c r="I13">
-        <v>0.21266699999999999</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="J13">
-        <v>3.2399999999999998E-2</v>
+        <v>7.5465070000000001</v>
       </c>
       <c r="K13">
-        <v>7.5465070000000001</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.983333</v>
       </c>
       <c r="M13">
-        <v>2.983333</v>
+        <v>1.122493</v>
       </c>
       <c r="N13">
-        <v>1.122493</v>
+        <v>11.136670000000001</v>
       </c>
       <c r="O13">
-        <v>11.136670000000001</v>
-      </c>
-      <c r="P13">
         <v>0.31044100000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
+      <c r="C14">
+        <v>68035</v>
+      </c>
       <c r="D14">
-        <v>68035</v>
+        <v>8180</v>
       </c>
       <c r="E14">
-        <v>8180</v>
+        <v>6261.6466104535029</v>
       </c>
       <c r="F14">
-        <v>6261.6466104535029</v>
+        <v>28.3</v>
       </c>
       <c r="G14">
-        <v>28.3</v>
+        <v>1594.400024</v>
       </c>
       <c r="H14">
-        <v>1594.400024</v>
+        <v>8.6</v>
       </c>
       <c r="I14">
-        <v>8.6</v>
+        <v>1.558729</v>
       </c>
       <c r="J14">
-        <v>1.558729</v>
+        <v>64.5</v>
       </c>
       <c r="K14">
-        <v>64.5</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M14">
-        <v>9.5</v>
+        <v>15.6</v>
       </c>
       <c r="N14">
-        <v>15.6</v>
+        <v>4.5927220000000002</v>
       </c>
       <c r="O14">
-        <v>4.5927220000000002</v>
-      </c>
-      <c r="P14">
         <v>0.58433900000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" t="s">
         <v>18</v>
       </c>
+      <c r="C15">
+        <v>68022</v>
+      </c>
       <c r="D15">
-        <v>68022</v>
+        <v>8180</v>
       </c>
       <c r="E15">
-        <v>8180</v>
+        <v>6261.6466104535029</v>
       </c>
       <c r="F15">
-        <v>6261.6466104535029</v>
+        <v>28.3</v>
       </c>
       <c r="G15">
-        <v>28.3</v>
+        <v>1493.286621</v>
       </c>
       <c r="H15">
-        <v>1493.286621</v>
+        <v>1.358333</v>
       </c>
       <c r="I15">
-        <v>1.358333</v>
+        <v>0.30810999999999999</v>
       </c>
       <c r="J15">
-        <v>0.30810999999999999</v>
+        <v>75.52628</v>
       </c>
       <c r="K15">
-        <v>75.52628</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.5833330000000001</v>
       </c>
       <c r="M15">
-        <v>2.5833330000000001</v>
+        <v>10.725390000000001</v>
       </c>
       <c r="N15">
-        <v>10.725390000000001</v>
+        <v>0.74707900000000005</v>
       </c>
       <c r="O15">
-        <v>0.74707900000000005</v>
-      </c>
-      <c r="P15">
         <v>0.23219999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" t="s">
         <v>19</v>
       </c>
+      <c r="C16">
+        <v>68039</v>
+      </c>
       <c r="D16">
-        <v>68039</v>
+        <v>1796.3279791561231</v>
       </c>
       <c r="E16">
-        <v>1796.3279791561231</v>
+        <v>1270.2118583465876</v>
       </c>
       <c r="F16">
-        <v>1270.2118583465876</v>
+        <v>9.4401215805471121</v>
       </c>
       <c r="G16">
-        <v>9.4401215805471121</v>
+        <v>1481.0067140000001</v>
       </c>
       <c r="H16">
-        <v>1481.0067140000001</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>86.813329999999993</v>
       </c>
       <c r="K16">
-        <v>86.813329999999993</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>0.23666699999999999</v>
       </c>
       <c r="M16">
-        <v>0.23666699999999999</v>
+        <v>0.43</v>
       </c>
       <c r="N16">
-        <v>0.43</v>
+        <v>1.576667</v>
       </c>
       <c r="O16">
-        <v>1.576667</v>
-      </c>
-      <c r="P16">
         <v>0.59150899999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" t="s">
         <v>21</v>
       </c>
+      <c r="C17">
+        <v>67039</v>
+      </c>
       <c r="D17">
-        <v>67039</v>
+        <v>1642.0833333333333</v>
       </c>
       <c r="E17">
-        <v>1642.0833333333333</v>
+        <v>2233.0833333333335</v>
       </c>
       <c r="F17">
-        <v>2233.0833333333335</v>
+        <v>11.427272727272724</v>
       </c>
       <c r="G17">
-        <v>11.427272727272724</v>
+        <v>1493.286621</v>
       </c>
       <c r="H17">
-        <v>1493.286621</v>
+        <v>1.358333</v>
       </c>
       <c r="I17">
-        <v>1.358333</v>
+        <v>0.30810999999999999</v>
       </c>
       <c r="J17">
-        <v>0.30810999999999999</v>
+        <v>75.52628</v>
       </c>
       <c r="K17">
-        <v>75.52628</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2.5833330000000001</v>
       </c>
       <c r="M17">
-        <v>2.5833330000000001</v>
+        <v>10.725390000000001</v>
       </c>
       <c r="N17">
-        <v>10.725390000000001</v>
+        <v>0.74707900000000005</v>
       </c>
       <c r="O17">
-        <v>0.74707900000000005</v>
-      </c>
-      <c r="P17">
         <v>0.46143200000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" t="s">
         <v>22</v>
       </c>
+      <c r="C18">
+        <v>67037</v>
+      </c>
       <c r="D18">
-        <v>67037</v>
+        <v>2571.75</v>
       </c>
       <c r="E18">
-        <v>2571.75</v>
+        <v>2039.3333333333333</v>
       </c>
       <c r="F18">
-        <v>2039.3333333333333</v>
+        <v>13.540000000000001</v>
       </c>
       <c r="G18">
-        <v>13.540000000000001</v>
+        <v>1542</v>
       </c>
       <c r="H18">
-        <v>1542</v>
+        <v>2.08</v>
       </c>
       <c r="I18">
-        <v>2.08</v>
+        <v>0.490566</v>
       </c>
       <c r="J18">
-        <v>0.490566</v>
+        <v>76.56</v>
       </c>
       <c r="K18">
-        <v>76.56</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M18">
-        <v>6.25</v>
+        <v>12.92</v>
       </c>
       <c r="N18">
-        <v>12.92</v>
+        <v>258.32</v>
       </c>
       <c r="O18">
-        <v>258.32</v>
-      </c>
-      <c r="P18">
         <v>1.998157</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" t="s">
         <v>23</v>
       </c>
+      <c r="C19">
+        <v>67001</v>
+      </c>
       <c r="D19">
-        <v>67001</v>
+        <v>9525</v>
       </c>
       <c r="E19">
-        <v>9525</v>
+        <v>1730.2020304029807</v>
       </c>
       <c r="F19">
-        <v>1730.2020304029807</v>
+        <v>10.5</v>
       </c>
       <c r="G19">
-        <v>10.5</v>
+        <v>1170.839966</v>
       </c>
       <c r="H19">
-        <v>1170.839966</v>
+        <v>3.93</v>
       </c>
       <c r="I19">
-        <v>3.93</v>
+        <v>1.959579</v>
       </c>
       <c r="J19">
-        <v>1.959579</v>
+        <v>51.3</v>
       </c>
       <c r="K19">
-        <v>51.3</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M19">
-        <v>3.25</v>
+        <v>10.74</v>
       </c>
       <c r="N19">
-        <v>10.74</v>
+        <v>1083.6559999999999</v>
       </c>
       <c r="O19">
-        <v>1083.6559999999999</v>
-      </c>
-      <c r="P19">
         <v>1.0369949999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" t="s">
         <v>24</v>
       </c>
+      <c r="C20">
+        <v>67062</v>
+      </c>
       <c r="D20">
-        <v>67062</v>
+        <v>2333.3333333333335</v>
       </c>
       <c r="E20">
-        <v>2333.3333333333335</v>
+        <v>26430.10495512934</v>
       </c>
       <c r="F20">
-        <v>26430.10495512934</v>
+        <v>46</v>
       </c>
       <c r="G20">
-        <v>46</v>
+        <v>1170.839966</v>
       </c>
       <c r="H20">
-        <v>1170.839966</v>
+        <v>3.93</v>
       </c>
       <c r="I20">
-        <v>3.93</v>
+        <v>1.959579</v>
       </c>
       <c r="J20">
-        <v>1.959579</v>
+        <v>51.3</v>
       </c>
       <c r="K20">
-        <v>51.3</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M20">
-        <v>3.25</v>
+        <v>10.74</v>
       </c>
       <c r="N20">
-        <v>10.74</v>
+        <v>1083.6559999999999</v>
       </c>
       <c r="O20">
-        <v>1083.6559999999999</v>
-      </c>
-      <c r="P20">
         <v>2.2855110000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" t="s">
         <v>25</v>
       </c>
+      <c r="C21">
+        <v>64011</v>
+      </c>
       <c r="D21">
-        <v>64011</v>
+        <v>5295</v>
       </c>
       <c r="E21">
-        <v>5295</v>
+        <v>503.31988193593691</v>
       </c>
       <c r="F21">
-        <v>503.31988193593691</v>
+        <v>41</v>
       </c>
       <c r="G21">
-        <v>41</v>
+        <v>1530</v>
       </c>
       <c r="H21">
-        <v>1530</v>
+        <v>1.97</v>
       </c>
       <c r="I21">
-        <v>1.97</v>
+        <v>0.53533299999999995</v>
       </c>
       <c r="J21">
-        <v>0.53533299999999995</v>
+        <v>76.622540000000001</v>
       </c>
       <c r="K21">
-        <v>76.622540000000001</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2.2966669999999998</v>
       </c>
       <c r="M21">
-        <v>2.2966669999999998</v>
+        <v>10.3208</v>
       </c>
       <c r="N21">
-        <v>10.3208</v>
+        <v>14.74</v>
       </c>
       <c r="O21">
-        <v>14.74</v>
-      </c>
-      <c r="P21">
         <v>0.50922999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" t="s">
         <v>26</v>
       </c>
+      <c r="C22">
+        <v>67057</v>
+      </c>
       <c r="D22">
-        <v>67057</v>
+        <v>3295</v>
       </c>
       <c r="E22">
-        <v>3295</v>
+        <v>588.35425044054443</v>
       </c>
       <c r="F22">
-        <v>588.35425044054443</v>
+        <v>3.7796942010068992</v>
       </c>
       <c r="G22">
-        <v>3.7796942010068992</v>
+        <v>1724</v>
       </c>
       <c r="H22">
-        <v>1724</v>
+        <v>15.07</v>
       </c>
       <c r="I22">
-        <v>15.07</v>
+        <v>2.9</v>
       </c>
       <c r="J22">
-        <v>2.9</v>
+        <v>62.05</v>
       </c>
       <c r="K22">
-        <v>62.05</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="M22">
-        <v>7.83</v>
+        <v>10.68</v>
       </c>
       <c r="N22">
-        <v>10.68</v>
+        <v>125.95</v>
       </c>
       <c r="O22">
-        <v>125.95</v>
-      </c>
-      <c r="P22">
         <v>1.9247240000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" t="s">
         <v>27</v>
       </c>
+      <c r="C23">
+        <v>64012</v>
+      </c>
       <c r="D23">
-        <v>64012</v>
+        <v>3200</v>
       </c>
       <c r="E23">
-        <v>3200</v>
+        <v>3977.5725722325878</v>
       </c>
       <c r="F23">
-        <v>3977.5725722325878</v>
+        <v>27.09194232168722</v>
       </c>
       <c r="G23">
-        <v>27.09194232168722</v>
+        <v>1798.0633539999999</v>
       </c>
       <c r="H23">
-        <v>1798.0633539999999</v>
+        <v>17.23667</v>
       </c>
       <c r="I23">
-        <v>17.23667</v>
+        <v>2.4739559999999998</v>
       </c>
       <c r="J23">
-        <v>2.4739559999999998</v>
+        <v>62.431649999999998</v>
       </c>
       <c r="K23">
-        <v>62.431649999999998</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="M23">
-        <v>5.61</v>
+        <v>8.7916799999999995</v>
       </c>
       <c r="N23">
-        <v>8.7916799999999995</v>
+        <v>1515.527</v>
       </c>
       <c r="O23">
-        <v>1515.527</v>
-      </c>
-      <c r="P23">
         <v>1.2780119999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" t="s">
         <v>28</v>
       </c>
+      <c r="C24">
+        <v>67012</v>
+      </c>
       <c r="D24">
-        <v>67012</v>
+        <v>7875</v>
       </c>
       <c r="E24">
-        <v>7875</v>
+        <v>7240.067882558219</v>
       </c>
       <c r="F24">
-        <v>7240.067882558219</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>19</v>
+        <v>1424.6093920000001</v>
       </c>
       <c r="H24">
-        <v>1424.6093920000001</v>
+        <v>0.62257799999999996</v>
       </c>
       <c r="I24">
-        <v>0.62257799999999996</v>
+        <v>0.273675</v>
       </c>
       <c r="J24">
-        <v>0.273675</v>
+        <v>40.98639</v>
       </c>
       <c r="K24">
-        <v>40.98639</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>8.4614010000000004</v>
       </c>
       <c r="M24">
-        <v>8.4614010000000004</v>
+        <v>45.93871</v>
       </c>
       <c r="N24">
-        <v>45.93871</v>
+        <v>997.70209999999997</v>
       </c>
       <c r="O24">
-        <v>997.70209999999997</v>
-      </c>
-      <c r="P24">
         <v>1.2303090000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" t="s">
         <v>29</v>
       </c>
+      <c r="C25">
+        <v>67041</v>
+      </c>
       <c r="D25">
-        <v>67041</v>
+        <v>2903</v>
       </c>
       <c r="E25">
-        <v>2903</v>
+        <v>1772</v>
       </c>
       <c r="F25">
-        <v>1772</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G25">
-        <v>10.397478991596639</v>
+        <v>1586.954956</v>
       </c>
       <c r="H25">
-        <v>1586.954956</v>
+        <v>0.85916700000000001</v>
       </c>
       <c r="I25">
-        <v>0.85916700000000001</v>
+        <v>0.29333300000000001</v>
       </c>
       <c r="J25">
-        <v>0.29333300000000001</v>
+        <v>87.071849999999998</v>
       </c>
       <c r="K25">
-        <v>87.071849999999998</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2.2479170000000002</v>
       </c>
       <c r="M25">
-        <v>2.2479170000000002</v>
+        <v>5.5985690000000004</v>
       </c>
       <c r="N25">
-        <v>5.5985690000000004</v>
+        <v>529.92830000000004</v>
       </c>
       <c r="O25">
-        <v>529.92830000000004</v>
-      </c>
-      <c r="P25">
         <v>1.3466670000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" t="s">
         <v>30</v>
       </c>
+      <c r="C26">
+        <v>67005</v>
+      </c>
       <c r="D26">
-        <v>67005</v>
+        <v>7875</v>
       </c>
       <c r="E26">
-        <v>7875</v>
+        <v>7240.067882558219</v>
       </c>
       <c r="F26">
-        <v>7240.067882558219</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>19</v>
+        <v>277.87728879999997</v>
       </c>
       <c r="H26">
-        <v>277.87728879999997</v>
+        <v>5.0110830000000002</v>
       </c>
       <c r="I26">
-        <v>5.0110830000000002</v>
+        <v>1.0106329999999999</v>
       </c>
       <c r="J26">
-        <v>1.0106329999999999</v>
+        <v>7.6571210000000001</v>
       </c>
       <c r="K26">
-        <v>7.6571210000000001</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>5.8883330000000003</v>
       </c>
       <c r="M26">
-        <v>5.8883330000000003</v>
+        <v>0.89947900000000003</v>
       </c>
       <c r="N26">
-        <v>0.89947900000000003</v>
+        <v>1.69425</v>
       </c>
       <c r="O26">
-        <v>1.69425</v>
-      </c>
-      <c r="P26">
         <v>0.65934700000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" t="s">
         <v>31</v>
       </c>
+      <c r="C27">
+        <v>67141</v>
+      </c>
       <c r="D27">
-        <v>67141</v>
+        <v>6272.2906885759003</v>
       </c>
       <c r="E27">
-        <v>6272.2906885759003</v>
+        <v>4954.3609397891696</v>
       </c>
       <c r="F27">
-        <v>4954.3609397891696</v>
+        <v>45.35</v>
       </c>
       <c r="G27">
-        <v>45.35</v>
+        <v>2415.719971</v>
       </c>
       <c r="H27">
-        <v>2415.719971</v>
+        <v>43.85</v>
       </c>
       <c r="I27">
-        <v>43.85</v>
+        <v>7.7830000000000004</v>
       </c>
       <c r="J27">
-        <v>7.7830000000000004</v>
+        <v>30.19</v>
       </c>
       <c r="K27">
-        <v>30.19</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M27">
-        <v>3.3</v>
+        <v>18.22</v>
       </c>
       <c r="N27">
-        <v>18.22</v>
+        <v>12</v>
       </c>
       <c r="O27">
-        <v>12</v>
-      </c>
-      <c r="P27">
         <v>8.0315030000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B28" t="s">
         <v>32</v>
       </c>
+      <c r="C28">
+        <v>77011</v>
+      </c>
       <c r="D28">
-        <v>77011</v>
+        <v>8180</v>
       </c>
       <c r="E28">
-        <v>8180</v>
+        <v>6261.6466104535029</v>
       </c>
       <c r="F28">
-        <v>6261.6466104535029</v>
+        <v>28.3</v>
       </c>
       <c r="G28">
-        <v>28.3</v>
+        <v>36.601112370000003</v>
       </c>
       <c r="H28">
-        <v>36.601112370000003</v>
+        <v>0.124444</v>
       </c>
       <c r="I28">
-        <v>0.124444</v>
+        <v>0.2</v>
       </c>
       <c r="J28">
-        <v>0.2</v>
+        <v>1.791256</v>
       </c>
       <c r="K28">
-        <v>1.791256</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.8722220000000001</v>
       </c>
       <c r="M28">
-        <v>1.8722220000000001</v>
+        <v>1.082077</v>
       </c>
       <c r="N28">
-        <v>1.082077</v>
+        <v>4.2044439999999996</v>
       </c>
       <c r="O28">
-        <v>4.2044439999999996</v>
-      </c>
-      <c r="P28">
         <v>1.0305</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>20</v>
       </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B29" t="s">
         <v>33</v>
       </c>
+      <c r="C29">
+        <v>67040</v>
+      </c>
       <c r="D29">
-        <v>67040</v>
+        <v>11000</v>
       </c>
       <c r="E29">
-        <v>11000</v>
+        <v>5596.804698945848</v>
       </c>
       <c r="F29">
-        <v>5596.804698945848</v>
+        <v>27.09194232168722</v>
       </c>
       <c r="G29">
-        <v>27.09194232168722</v>
+        <v>114.6600037</v>
       </c>
       <c r="H29">
-        <v>114.6600037</v>
+        <v>0.54666700000000001</v>
       </c>
       <c r="I29">
-        <v>0.54666700000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J29">
-        <v>0.12</v>
+        <v>4.3334780000000004</v>
       </c>
       <c r="K29">
-        <v>4.3334780000000004</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M29">
-        <v>3.12</v>
+        <v>2.8731879999999999</v>
       </c>
       <c r="N29">
-        <v>2.8731879999999999</v>
+        <v>9.0854999999999997</v>
       </c>
       <c r="O29">
-        <v>9.0854999999999997</v>
-      </c>
-      <c r="P29">
         <v>0.67259199999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>20</v>
       </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" t="s">
         <v>34</v>
       </c>
+      <c r="C30">
+        <v>67045</v>
+      </c>
       <c r="D30">
-        <v>67045</v>
+        <v>14500</v>
       </c>
       <c r="E30">
-        <v>14500</v>
+        <v>12800</v>
       </c>
       <c r="F30">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G30">
-        <v>52</v>
+        <v>82.128890990000002</v>
       </c>
       <c r="H30">
-        <v>82.128890990000002</v>
+        <v>0.14111099999999999</v>
       </c>
       <c r="I30">
-        <v>0.14111099999999999</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="J30">
-        <v>4.7600000000000003E-2</v>
+        <v>4.4199520000000003</v>
       </c>
       <c r="K30">
-        <v>4.4199520000000003</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.923333</v>
       </c>
       <c r="M30">
-        <v>1.923333</v>
+        <v>1.122271</v>
       </c>
       <c r="N30">
-        <v>1.122271</v>
+        <v>3.3216670000000001</v>
       </c>
       <c r="O30">
-        <v>3.3216670000000001</v>
-      </c>
-      <c r="P30">
         <v>0.246141</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>20</v>
       </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" t="s">
         <v>35</v>
       </c>
+      <c r="C31">
+        <v>67009</v>
+      </c>
       <c r="D31">
-        <v>67009</v>
+        <v>9525</v>
       </c>
       <c r="E31">
-        <v>9525</v>
+        <v>1730.2020304029807</v>
       </c>
       <c r="F31">
-        <v>1730.2020304029807</v>
+        <v>10.5</v>
       </c>
       <c r="G31">
-        <v>10.5</v>
+        <v>138.54861450000001</v>
       </c>
       <c r="H31">
-        <v>138.54861450000001</v>
+        <v>0.42583300000000002</v>
       </c>
       <c r="I31">
-        <v>0.42583300000000002</v>
+        <v>0.06</v>
       </c>
       <c r="J31">
-        <v>0.06</v>
+        <v>5.840363</v>
       </c>
       <c r="K31">
-        <v>5.840363</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2.6475</v>
       </c>
       <c r="M31">
-        <v>2.6475</v>
+        <v>2.7843599999999999</v>
       </c>
       <c r="N31">
-        <v>2.7843599999999999</v>
+        <v>2.3216670000000001</v>
       </c>
       <c r="O31">
-        <v>2.3216670000000001</v>
-      </c>
-      <c r="P31">
         <v>1.7047410000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" t="s">
         <v>36</v>
       </c>
+      <c r="C32">
+        <v>85008</v>
+      </c>
       <c r="D32">
-        <v>85008</v>
+        <v>9525</v>
       </c>
       <c r="E32">
-        <v>9525</v>
+        <v>1730.2020304029807</v>
       </c>
       <c r="F32">
-        <v>1730.2020304029807</v>
+        <v>10.5</v>
       </c>
       <c r="G32">
-        <v>10.5</v>
+        <v>73.088333129999995</v>
       </c>
       <c r="H32">
-        <v>73.088333129999995</v>
+        <v>0.12</v>
       </c>
       <c r="I32">
-        <v>0.12</v>
+        <v>3.1E-2</v>
       </c>
       <c r="J32">
-        <v>3.1E-2</v>
+        <v>3.7110150000000002</v>
       </c>
       <c r="K32">
-        <v>3.7110150000000002</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.2816669999999999</v>
       </c>
       <c r="M32">
-        <v>1.2816669999999999</v>
+        <v>1.005652</v>
       </c>
       <c r="N32">
-        <v>1.005652</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
         <v>0.33213399999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>20</v>
       </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" t="s">
         <v>37</v>
       </c>
+      <c r="C33">
+        <v>85084</v>
+      </c>
       <c r="D33">
-        <v>85084</v>
+        <v>1796.3279791561231</v>
       </c>
       <c r="E33">
-        <v>1796.3279791561231</v>
+        <v>1270.2118583465876</v>
       </c>
       <c r="F33">
-        <v>1270.2118583465876</v>
+        <v>9.4401215805471121</v>
       </c>
       <c r="G33">
-        <v>9.4401215805471121</v>
+        <v>92.008934019999998</v>
       </c>
       <c r="H33">
-        <v>92.008934019999998</v>
+        <v>0.183333</v>
       </c>
       <c r="I33">
-        <v>0.183333</v>
+        <v>0.04</v>
       </c>
       <c r="J33">
-        <v>0.04</v>
+        <v>5.0293900000000002</v>
       </c>
       <c r="K33">
-        <v>5.0293900000000002</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2.0160670000000001</v>
       </c>
       <c r="M33">
-        <v>2.0160670000000001</v>
+        <v>1.05121</v>
       </c>
       <c r="N33">
-        <v>1.05121</v>
+        <v>0.18925</v>
       </c>
       <c r="O33">
-        <v>0.18925</v>
-      </c>
-      <c r="P33">
         <v>0.29757800000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>20</v>
       </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" t="s">
         <v>38</v>
       </c>
+      <c r="C34">
+        <v>70084</v>
+      </c>
       <c r="D34">
-        <v>70084</v>
+        <v>2420.7630976893161</v>
       </c>
       <c r="E34">
-        <v>2420.7630976893161</v>
+        <v>1730.2020304029807</v>
       </c>
       <c r="F34">
-        <v>1730.2020304029807</v>
+        <v>10.5</v>
       </c>
       <c r="G34">
-        <v>10.5</v>
+        <v>43.828887940000001</v>
       </c>
       <c r="H34">
-        <v>43.828887940000001</v>
+        <v>0.09</v>
       </c>
       <c r="I34">
-        <v>0.09</v>
+        <v>3.0273000000000001E-2</v>
       </c>
       <c r="J34">
-        <v>3.0273000000000001E-2</v>
+        <v>2.2345890000000002</v>
       </c>
       <c r="K34">
-        <v>2.2345890000000002</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.036667</v>
       </c>
       <c r="M34">
-        <v>1.036667</v>
+        <v>0.69652199999999997</v>
       </c>
       <c r="N34">
-        <v>0.69652199999999997</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
         <v>0.34414</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B35" t="s">
         <v>39</v>
       </c>
+      <c r="C35">
+        <v>67051</v>
+      </c>
       <c r="D35">
-        <v>67051</v>
+        <v>2903</v>
       </c>
       <c r="E35">
-        <v>2903</v>
+        <v>1772</v>
       </c>
       <c r="F35">
-        <v>1772</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G35">
-        <v>10.397478991596639</v>
+        <v>75.511665339999993</v>
       </c>
       <c r="H35">
-        <v>75.511665339999993</v>
+        <v>5.5E-2</v>
       </c>
       <c r="I35">
-        <v>5.5E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="J35">
-        <v>1.29E-2</v>
+        <v>4.1736959999999996</v>
       </c>
       <c r="K35">
-        <v>4.1736959999999996</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M35">
-        <v>1.4</v>
+        <v>0.88963800000000004</v>
       </c>
       <c r="N35">
-        <v>0.88963800000000004</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
         <v>0.22817699999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B36" t="s">
         <v>41</v>
       </c>
+      <c r="C36">
+        <v>63002</v>
+      </c>
       <c r="D36">
-        <v>63002</v>
+        <v>930</v>
       </c>
       <c r="E36">
-        <v>930</v>
+        <v>1270.2118583465876</v>
       </c>
       <c r="F36">
-        <v>1270.2118583465876</v>
+        <v>9.4401215805471121</v>
       </c>
       <c r="G36">
-        <v>9.4401215805471121</v>
+        <v>102.837738</v>
       </c>
       <c r="H36">
-        <v>102.837738</v>
+        <v>0.27190500000000001</v>
       </c>
       <c r="I36">
-        <v>0.27190500000000001</v>
+        <v>4.9174000000000002E-2</v>
       </c>
       <c r="J36">
-        <v>4.9174000000000002E-2</v>
+        <v>5.2459210000000001</v>
       </c>
       <c r="K36">
-        <v>5.2459210000000001</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.674167</v>
       </c>
       <c r="M36">
-        <v>1.674167</v>
+        <v>1.097888</v>
       </c>
       <c r="N36">
-        <v>1.097888</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
         <v>0.58134399999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37">
-        <v>3</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B37" t="s">
         <v>42</v>
       </c>
+      <c r="C37">
+        <v>63001</v>
+      </c>
       <c r="D37">
-        <v>63001</v>
+        <v>11300</v>
       </c>
       <c r="E37">
-        <v>11300</v>
+        <v>10000</v>
       </c>
       <c r="F37">
-        <v>10000</v>
+        <v>52</v>
       </c>
       <c r="G37">
-        <v>52</v>
+        <v>74.343223570000006</v>
       </c>
       <c r="H37">
-        <v>74.343223570000006</v>
+        <v>0.16777800000000001</v>
       </c>
       <c r="I37">
-        <v>0.16777800000000001</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J37">
-        <v>2.4E-2</v>
+        <v>3.817475</v>
       </c>
       <c r="K37">
-        <v>3.817475</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.5972219999999999</v>
       </c>
       <c r="M37">
-        <v>1.5972219999999999</v>
+        <v>1.036081</v>
       </c>
       <c r="N37">
-        <v>1.036081</v>
+        <v>3.1315</v>
       </c>
       <c r="O37">
-        <v>3.1315</v>
-      </c>
-      <c r="P37">
         <v>0.46989300000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38">
-        <v>3</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B38" t="s">
         <v>43</v>
       </c>
+      <c r="C38">
+        <v>65097</v>
+      </c>
       <c r="D38">
-        <v>65097</v>
+        <v>8762.4166666666661</v>
       </c>
       <c r="E38">
-        <v>8762.4166666666661</v>
+        <v>5965.8796627210149</v>
       </c>
       <c r="F38">
-        <v>5965.8796627210149</v>
+        <v>41.388095238095239</v>
       </c>
       <c r="G38">
-        <v>41.388095238095239</v>
+        <v>172.85333249999999</v>
       </c>
       <c r="H38">
-        <v>172.85333249999999</v>
+        <v>0.13</v>
       </c>
       <c r="I38">
-        <v>0.13</v>
+        <v>5.4600000000000003E-2</v>
       </c>
       <c r="J38">
-        <v>5.4600000000000003E-2</v>
+        <v>9.2065940000000008</v>
       </c>
       <c r="K38">
-        <v>9.2065940000000008</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>2.0433330000000001</v>
       </c>
       <c r="M38">
-        <v>2.0433330000000001</v>
+        <v>1.7600720000000001</v>
       </c>
       <c r="N38">
-        <v>1.7600720000000001</v>
+        <v>0.623</v>
       </c>
       <c r="O38">
-        <v>0.623</v>
-      </c>
-      <c r="P38">
         <v>0.27027299999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
-        <v>3</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B39" t="s">
         <v>44</v>
       </c>
+      <c r="C39">
+        <v>65010</v>
+      </c>
       <c r="D39">
-        <v>65010</v>
+        <v>8762.4166666666661</v>
       </c>
       <c r="E39">
-        <v>8762.4166666666661</v>
+        <v>5965.8796627210149</v>
       </c>
       <c r="F39">
-        <v>5965.8796627210149</v>
+        <v>41.388095238095239</v>
       </c>
       <c r="G39">
-        <v>41.388095238095239</v>
+        <v>513.57446289999996</v>
       </c>
       <c r="H39">
-        <v>513.57446289999996</v>
+        <v>0.20333300000000001</v>
       </c>
       <c r="I39">
-        <v>0.20333300000000001</v>
+        <v>3.56E-2</v>
       </c>
       <c r="J39">
-        <v>3.56E-2</v>
+        <v>25.758600000000001</v>
       </c>
       <c r="K39">
-        <v>25.758600000000001</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>3.1944439999999998</v>
       </c>
       <c r="M39">
-        <v>3.1944439999999998</v>
+        <v>5.7002899999999999</v>
       </c>
       <c r="N39">
-        <v>5.7002899999999999</v>
+        <v>5.4260000000000002</v>
       </c>
       <c r="O39">
-        <v>5.4260000000000002</v>
-      </c>
-      <c r="P39">
         <v>1.686687</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B40" t="s">
         <v>45</v>
       </c>
+      <c r="C40">
+        <v>65016</v>
+      </c>
       <c r="D40">
-        <v>65016</v>
+        <v>1547</v>
       </c>
       <c r="E40">
-        <v>1547</v>
+        <v>2462</v>
       </c>
       <c r="F40">
-        <v>2462</v>
+        <v>11.5</v>
       </c>
       <c r="G40">
-        <v>11.5</v>
+        <v>43</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>0.16</v>
       </c>
       <c r="I40">
-        <v>0.16</v>
+        <v>0.21333299999999999</v>
       </c>
       <c r="J40">
-        <v>0.21333299999999999</v>
+        <v>1.6955070000000001</v>
       </c>
       <c r="K40">
-        <v>1.6955070000000001</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1.826667</v>
       </c>
       <c r="M40">
-        <v>1.826667</v>
+        <v>1.347826</v>
       </c>
       <c r="N40">
-        <v>1.347826</v>
+        <v>3.38</v>
       </c>
       <c r="O40">
-        <v>3.38</v>
-      </c>
-      <c r="P40">
         <v>1.6317090000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B41" t="s">
         <v>46</v>
       </c>
+      <c r="C41">
+        <v>65015</v>
+      </c>
       <c r="D41">
-        <v>65015</v>
+        <v>10200</v>
       </c>
       <c r="E41">
-        <v>10200</v>
+        <v>7359.5180236216484</v>
       </c>
       <c r="F41">
-        <v>7359.5180236216484</v>
+        <v>19</v>
       </c>
       <c r="G41">
-        <v>19</v>
+        <v>452.65499879999999</v>
       </c>
       <c r="H41">
-        <v>452.65499879999999</v>
+        <v>0.28249999999999997</v>
       </c>
       <c r="I41">
-        <v>0.28249999999999997</v>
+        <v>9.3299999999999994E-2</v>
       </c>
       <c r="J41">
-        <v>9.3299999999999994E-2</v>
+        <v>25.933440000000001</v>
       </c>
       <c r="K41">
-        <v>25.933440000000001</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.9466669999999999</v>
       </c>
       <c r="M41">
-        <v>1.9466669999999999</v>
+        <v>1.1090580000000001</v>
       </c>
       <c r="N41">
-        <v>1.1090580000000001</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
         <v>0.389376</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
-        <v>3</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B42" t="s">
         <v>47</v>
       </c>
+      <c r="C42">
+        <v>65002</v>
+      </c>
       <c r="D42">
-        <v>65002</v>
+        <v>2903</v>
       </c>
       <c r="E42">
-        <v>2903</v>
+        <v>1772</v>
       </c>
       <c r="F42">
-        <v>1772</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G42">
-        <v>10.397478991596639</v>
+        <v>190.27867130000001</v>
       </c>
       <c r="H42">
-        <v>190.27867130000001</v>
+        <v>0.24222199999999999</v>
       </c>
       <c r="I42">
-        <v>0.24222199999999999</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>10.83136</v>
       </c>
       <c r="K42">
-        <v>10.83136</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>2.0196299999999998</v>
       </c>
       <c r="M42">
-        <v>2.0196299999999998</v>
+        <v>0.90352699999999997</v>
       </c>
       <c r="N42">
-        <v>0.90352699999999997</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="O42">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="P42">
         <v>0.215112</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>40</v>
       </c>
-      <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" t="s">
         <v>48</v>
       </c>
+      <c r="C43">
+        <v>65033</v>
+      </c>
       <c r="D43">
-        <v>65033</v>
+        <v>808.33</v>
       </c>
       <c r="E43">
-        <v>808.33</v>
+        <v>5128.8970172703139</v>
       </c>
       <c r="F43">
-        <v>5128.8970172703139</v>
+        <v>5.52</v>
       </c>
       <c r="G43">
-        <v>5.52</v>
+        <v>94.718330379999998</v>
       </c>
       <c r="H43">
-        <v>94.718330379999998</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>5.2466660000000003</v>
       </c>
       <c r="K43">
-        <v>5.2466660000000003</v>
+        <v>0</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="N43">
-        <v>0.32500000000000001</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
         <v>0.39804099999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44">
-        <v>3</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B44" t="s">
         <v>49</v>
       </c>
+      <c r="C44">
+        <v>80001</v>
+      </c>
       <c r="D44">
-        <v>80001</v>
+        <v>2350</v>
       </c>
       <c r="E44">
-        <v>2350</v>
+        <v>6114.9086447857417</v>
       </c>
       <c r="F44">
-        <v>6114.9086447857417</v>
+        <v>33.5</v>
       </c>
       <c r="G44">
-        <v>33.5</v>
+        <v>170.88333130000001</v>
       </c>
       <c r="H44">
-        <v>170.88333130000001</v>
+        <v>7.3332999999999995E-2</v>
       </c>
       <c r="I44">
-        <v>7.3332999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>9.5421739999999993</v>
       </c>
       <c r="K44">
-        <v>9.5421739999999993</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="M44">
-        <v>0.94</v>
+        <v>0.84782599999999997</v>
       </c>
       <c r="N44">
-        <v>0.84782599999999997</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
         <v>0.28998200000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" t="s">
         <v>51</v>
       </c>
+      <c r="C45">
+        <v>79039</v>
+      </c>
       <c r="D45">
-        <v>79039</v>
+        <v>2571.75</v>
       </c>
       <c r="E45">
-        <v>2571.75</v>
+        <v>2039.3333333333333</v>
       </c>
       <c r="F45">
-        <v>2039.3333333333333</v>
+        <v>13.540000000000001</v>
       </c>
       <c r="G45">
-        <v>13.540000000000001</v>
+        <v>211.2668304</v>
       </c>
       <c r="H45">
-        <v>211.2668304</v>
+        <v>0.33333299999999999</v>
       </c>
       <c r="I45">
-        <v>0.33333299999999999</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="J45">
-        <v>2.2800000000000001E-2</v>
+        <v>11.61347</v>
       </c>
       <c r="K45">
-        <v>11.61347</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1.1166670000000001</v>
       </c>
       <c r="M45">
-        <v>1.1166670000000001</v>
+        <v>0.679674</v>
       </c>
       <c r="N45">
-        <v>0.679674</v>
+        <v>2.84</v>
       </c>
       <c r="O45">
-        <v>2.84</v>
-      </c>
-      <c r="P45">
         <v>0.24232500000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B46" t="s">
         <v>52</v>
       </c>
+      <c r="C46">
+        <v>79006</v>
+      </c>
       <c r="D46">
-        <v>79006</v>
+        <v>1245</v>
       </c>
       <c r="E46">
-        <v>1245</v>
+        <v>452.50899863661198</v>
       </c>
       <c r="F46">
-        <v>452.50899863661198</v>
+        <v>4.5</v>
       </c>
       <c r="G46">
-        <v>4.5</v>
+        <v>270.54934689999999</v>
       </c>
       <c r="H46">
-        <v>270.54934689999999</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="I46">
-        <v>0.49099999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J46">
-        <v>0.2</v>
+        <v>15.65189</v>
       </c>
       <c r="K46">
-        <v>15.65189</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>2.0705</v>
       </c>
       <c r="M46">
-        <v>2.0705</v>
+        <v>0.29027799999999998</v>
       </c>
       <c r="N46">
-        <v>0.29027799999999998</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="O46">
-        <v>0.65900000000000003</v>
-      </c>
-      <c r="P46">
         <v>0.44255699999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
-      <c r="B47">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B47" t="s">
         <v>53</v>
       </c>
+      <c r="C47">
+        <v>79088</v>
+      </c>
       <c r="D47">
-        <v>79088</v>
+        <v>794.44444444444446</v>
       </c>
       <c r="E47">
-        <v>794.44444444444446</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F47">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G47">
-        <v>57.5</v>
+        <v>184.74646000000001</v>
       </c>
       <c r="H47">
-        <v>184.74646000000001</v>
+        <v>0.25286700000000001</v>
       </c>
       <c r="I47">
-        <v>0.25286700000000001</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="J47">
-        <v>8.1000000000000003E-2</v>
+        <v>10.71691</v>
       </c>
       <c r="K47">
-        <v>10.71691</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1.828667</v>
       </c>
       <c r="M47">
-        <v>1.828667</v>
+        <v>0.56829300000000005</v>
       </c>
       <c r="N47">
-        <v>0.56829300000000005</v>
+        <v>2.4434999999999998</v>
       </c>
       <c r="O47">
-        <v>2.4434999999999998</v>
-      </c>
-      <c r="P47">
         <v>0.329457</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
-      <c r="B48">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" t="s">
         <v>54</v>
       </c>
+      <c r="C48">
+        <v>79037</v>
+      </c>
       <c r="D48">
-        <v>79037</v>
+        <v>6025</v>
       </c>
       <c r="E48">
-        <v>6025</v>
+        <v>4218.3167817482954</v>
       </c>
       <c r="F48">
-        <v>4218.3167817482954</v>
+        <v>115</v>
       </c>
       <c r="G48">
-        <v>115</v>
+        <v>272.6580811</v>
       </c>
       <c r="H48">
-        <v>272.6580811</v>
+        <v>0.3145</v>
       </c>
       <c r="I48">
-        <v>0.3145</v>
+        <v>0.1</v>
       </c>
       <c r="J48">
-        <v>0.1</v>
+        <v>15.958959999999999</v>
       </c>
       <c r="K48">
-        <v>15.958959999999999</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>2.1404999999999998</v>
       </c>
       <c r="M48">
-        <v>2.1404999999999998</v>
+        <v>0.52845600000000004</v>
       </c>
       <c r="N48">
-        <v>0.52845600000000004</v>
+        <v>0.918933</v>
       </c>
       <c r="O48">
-        <v>0.918933</v>
-      </c>
-      <c r="P48">
         <v>0.36564000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
-      <c r="B49">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B49" t="s">
         <v>55</v>
       </c>
+      <c r="C49">
+        <v>79032</v>
+      </c>
       <c r="D49">
-        <v>79032</v>
+        <v>2571.0720128824478</v>
       </c>
       <c r="E49">
-        <v>2571.0720128824478</v>
+        <v>4399.5</v>
       </c>
       <c r="F49">
-        <v>4399.5</v>
+        <v>59.805555555555564</v>
       </c>
       <c r="G49">
-        <v>59.805555555555564</v>
+        <v>123.6633301</v>
       </c>
       <c r="H49">
-        <v>123.6633301</v>
+        <v>5.5E-2</v>
       </c>
       <c r="I49">
-        <v>5.5E-2</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>6.5246380000000004</v>
       </c>
       <c r="K49">
-        <v>6.5246380000000004</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>0.126667</v>
       </c>
       <c r="M49">
-        <v>0.126667</v>
+        <v>0.69702900000000001</v>
       </c>
       <c r="N49">
-        <v>0.69702900000000001</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
         <v>0.165829</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B50">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B50" t="s">
         <v>56</v>
       </c>
+      <c r="C50">
+        <v>79030</v>
+      </c>
       <c r="D50">
-        <v>79030</v>
+        <v>260.2</v>
       </c>
       <c r="E50">
-        <v>260.2</v>
+        <v>159.54554321033251</v>
       </c>
       <c r="F50">
-        <v>159.54554321033251</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G50">
-        <v>4.1470096879308791</v>
+        <v>102</v>
       </c>
       <c r="H50">
-        <v>102</v>
+        <v>0.15</v>
       </c>
       <c r="I50">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="J50">
-        <v>0.04</v>
+        <v>5.7</v>
       </c>
       <c r="K50">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M50">
-        <v>1.22</v>
+        <v>0.61</v>
       </c>
       <c r="N50">
-        <v>0.61</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="O50">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="P50">
         <v>0.34121299999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
-      <c r="B51">
-        <v>5</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B51" t="s">
         <v>58</v>
       </c>
+      <c r="C51">
+        <v>63010</v>
+      </c>
       <c r="D51">
-        <v>63010</v>
+        <v>1853.3333</v>
       </c>
       <c r="E51">
-        <v>1853.3333</v>
+        <v>928.18059000000005</v>
       </c>
       <c r="F51">
-        <v>928.18059000000005</v>
+        <v>4.1470096999999999</v>
       </c>
       <c r="G51">
-        <v>4.1470096999999999</v>
+        <v>241.500946</v>
       </c>
       <c r="H51">
-        <v>241.500946</v>
+        <v>0.20338899999999999</v>
       </c>
       <c r="I51">
-        <v>0.20338899999999999</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="J51">
-        <v>6.7500000000000004E-2</v>
+        <v>13.706490000000001</v>
       </c>
       <c r="K51">
-        <v>13.706490000000001</v>
+        <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>0.92683300000000002</v>
       </c>
       <c r="M51">
-        <v>0.92683300000000002</v>
+        <v>0.54745200000000005</v>
       </c>
       <c r="N51">
-        <v>0.54745200000000005</v>
+        <v>3.9594999999999998</v>
       </c>
       <c r="O51">
-        <v>3.9594999999999998</v>
-      </c>
-      <c r="P51">
         <v>0.86650799999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
-      <c r="B52">
-        <v>5</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B52" t="s">
         <v>59</v>
       </c>
+      <c r="C52">
+        <v>69033</v>
+      </c>
       <c r="D52">
-        <v>69033</v>
+        <v>942.55692023243523</v>
       </c>
       <c r="E52">
-        <v>942.55692023243523</v>
+        <v>681.0770230540021</v>
       </c>
       <c r="F52">
-        <v>681.0770230540021</v>
+        <v>7.2333333333333334</v>
       </c>
       <c r="G52">
-        <v>7.2333333333333334</v>
+        <v>94.718330379999998</v>
       </c>
       <c r="H52">
-        <v>94.718330379999998</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>5.2466660000000003</v>
       </c>
       <c r="K52">
-        <v>5.2466660000000003</v>
+        <v>0</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="N52">
-        <v>0.32500000000000001</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
         <v>0.41017399999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>57</v>
       </c>
-      <c r="B53">
-        <v>5</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B53" t="s">
         <v>60</v>
       </c>
+      <c r="C53">
+        <v>72601</v>
+      </c>
       <c r="D53">
-        <v>72601</v>
+        <v>953.75</v>
       </c>
       <c r="E53">
-        <v>953.75</v>
+        <v>1003.3165478759558</v>
       </c>
       <c r="F53">
-        <v>1003.3165478759558</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G53">
-        <v>4.1470096879308791</v>
+        <v>878.23333330000003</v>
       </c>
       <c r="H53">
-        <v>878.23333330000003</v>
+        <v>10.133330000000001</v>
       </c>
       <c r="I53">
-        <v>10.133330000000001</v>
+        <v>6.26</v>
       </c>
       <c r="J53">
-        <v>6.26</v>
+        <v>26.6</v>
       </c>
       <c r="K53">
-        <v>26.6</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>0.93333299999999997</v>
       </c>
       <c r="M53">
-        <v>0.93333299999999997</v>
+        <v>3.5</v>
       </c>
       <c r="N53">
-        <v>3.5</v>
+        <v>60</v>
       </c>
       <c r="O53">
-        <v>60</v>
-      </c>
-      <c r="P53">
         <v>1.0177700000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>195</v>
       </c>
-      <c r="B54">
-        <v>5</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B54" t="s">
         <v>61</v>
       </c>
+      <c r="C54">
+        <v>66025</v>
+      </c>
       <c r="D54">
-        <v>66025</v>
+        <v>719.03072599531617</v>
       </c>
       <c r="E54">
-        <v>719.03072599531617</v>
+        <v>3082.4359757713787</v>
       </c>
       <c r="F54">
-        <v>3082.4359757713787</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G54">
-        <v>4.1470096879308791</v>
+        <v>1627.4</v>
       </c>
       <c r="H54">
-        <v>1627.4</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="J54">
-        <v>4.2000000000000003E-2</v>
+        <v>97</v>
       </c>
       <c r="K54">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M54">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="P54">
         <v>2.3394509999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>195</v>
       </c>
-      <c r="B55">
-        <v>5</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" t="s">
         <v>62</v>
       </c>
+      <c r="C55">
+        <v>63012</v>
+      </c>
       <c r="D55">
-        <v>63012</v>
+        <v>257.66666666666669</v>
       </c>
       <c r="E55">
-        <v>257.66666666666669</v>
+        <v>395.18339294745317</v>
       </c>
       <c r="F55">
-        <v>395.18339294745317</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G55">
-        <v>4.1470096879308791</v>
+        <v>2116.6665520000001</v>
       </c>
       <c r="H55">
-        <v>2116.6665520000001</v>
+        <v>24.848970000000001</v>
       </c>
       <c r="I55">
-        <v>24.848970000000001</v>
+        <v>14.367520000000001</v>
       </c>
       <c r="J55">
-        <v>14.367520000000001</v>
+        <v>66.813789999999997</v>
       </c>
       <c r="K55">
-        <v>66.813789999999997</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1.786897</v>
       </c>
       <c r="M55">
-        <v>1.786897</v>
+        <v>4.5589659999999999</v>
       </c>
       <c r="N55">
-        <v>4.5589659999999999</v>
+        <v>76.154769999999999</v>
       </c>
       <c r="O55">
-        <v>76.154769999999999</v>
-      </c>
-      <c r="P55">
         <v>2.867731</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>195</v>
       </c>
-      <c r="B56">
-        <v>5</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" t="s">
         <v>63</v>
       </c>
+      <c r="C56">
+        <v>63021</v>
+      </c>
       <c r="D56">
-        <v>63021</v>
+        <v>80</v>
       </c>
       <c r="E56">
-        <v>80</v>
+        <v>537.13215311199122</v>
       </c>
       <c r="F56">
-        <v>537.13215311199122</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G56">
-        <v>4.1470096879308791</v>
+        <v>289.82333369999998</v>
       </c>
       <c r="H56">
-        <v>289.82333369999998</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>16.880140000000001</v>
       </c>
       <c r="K56">
-        <v>16.880140000000001</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1.016667</v>
       </c>
       <c r="M56">
-        <v>1.016667</v>
+        <v>0.70652199999999998</v>
       </c>
       <c r="N56">
-        <v>0.70652199999999998</v>
+        <v>3.2010000000000001</v>
       </c>
       <c r="O56">
-        <v>3.2010000000000001</v>
-      </c>
-      <c r="P56">
         <v>1.4965360000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>195</v>
       </c>
-      <c r="B57">
-        <v>5</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B57" t="s">
         <v>64</v>
       </c>
+      <c r="C57">
+        <v>78033</v>
+      </c>
       <c r="D57">
-        <v>78033</v>
+        <v>80</v>
       </c>
       <c r="E57">
-        <v>80</v>
+        <v>537.13215311199122</v>
       </c>
       <c r="F57">
-        <v>537.13215311199122</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G57">
-        <v>4.1470096879308791</v>
+        <v>1374.177124</v>
       </c>
       <c r="H57">
-        <v>1374.177124</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>80.93777</v>
       </c>
       <c r="K57">
-        <v>80.93777</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>0.19612099999999999</v>
       </c>
       <c r="M57">
-        <v>0.19612099999999999</v>
+        <v>0.17</v>
       </c>
       <c r="N57">
-        <v>0.17</v>
+        <v>6.0563339999999997</v>
       </c>
       <c r="O57">
-        <v>6.0563339999999997</v>
-      </c>
-      <c r="P57">
         <v>2.6127989999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>195</v>
       </c>
-      <c r="B58">
-        <v>5</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="B58" t="s">
         <v>65</v>
       </c>
+      <c r="C58">
+        <v>78003</v>
+      </c>
       <c r="D58">
-        <v>78003</v>
+        <v>238.3640444444444</v>
       </c>
       <c r="E58">
-        <v>238.3640444444444</v>
+        <v>174.29743903085512</v>
       </c>
       <c r="F58">
-        <v>174.29743903085512</v>
+        <v>1.0017757009345793</v>
       </c>
       <c r="G58">
-        <v>1.0017757009345793</v>
+        <v>1279.1199999999999</v>
       </c>
       <c r="H58">
-        <v>1279.1199999999999</v>
+        <v>1.0409999999999999</v>
       </c>
       <c r="I58">
-        <v>1.0409999999999999</v>
+        <v>0.35220000000000001</v>
       </c>
       <c r="J58">
-        <v>0.35220000000000001</v>
+        <v>72.555999999999997</v>
       </c>
       <c r="K58">
-        <v>72.555999999999997</v>
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>5.3159999999999998</v>
       </c>
       <c r="M58">
-        <v>5.3159999999999998</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="N58">
-        <v>3.2349999999999999</v>
+        <v>45.054000000000002</v>
       </c>
       <c r="O58">
-        <v>45.054000000000002</v>
-      </c>
-      <c r="P58">
         <v>3.2630889999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>195</v>
       </c>
-      <c r="B59">
-        <v>5</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B59" t="s">
         <v>66</v>
       </c>
+      <c r="C59">
+        <v>72002</v>
+      </c>
       <c r="D59">
-        <v>72002</v>
+        <v>1020</v>
       </c>
       <c r="E59">
-        <v>1020</v>
+        <v>237.90824017990215</v>
       </c>
       <c r="F59">
-        <v>237.90824017990215</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G59">
-        <v>4.1470096879308791</v>
+        <v>2590.241211</v>
       </c>
       <c r="H59">
-        <v>2590.241211</v>
+        <v>51.797780000000003</v>
       </c>
       <c r="I59">
-        <v>51.797780000000003</v>
+        <v>9.74</v>
       </c>
       <c r="J59">
-        <v>9.74</v>
+        <v>16.86749</v>
       </c>
       <c r="K59">
-        <v>16.86749</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>8.9944450000000007</v>
       </c>
       <c r="M59">
-        <v>8.9944450000000007</v>
+        <v>27.52506</v>
       </c>
       <c r="N59">
-        <v>27.52506</v>
+        <v>375.73270000000002</v>
       </c>
       <c r="O59">
-        <v>375.73270000000002</v>
-      </c>
-      <c r="P59">
         <v>1.90933</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>195</v>
       </c>
-      <c r="B60">
-        <v>5</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B60" t="s">
         <v>67</v>
       </c>
+      <c r="C60">
+        <v>74082</v>
+      </c>
       <c r="D60">
-        <v>74082</v>
+        <v>89.5</v>
       </c>
       <c r="E60">
-        <v>89.5</v>
+        <v>933.05512564940193</v>
       </c>
       <c r="F60">
-        <v>933.05512564940193</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G60">
-        <v>4.1470096879308791</v>
+        <v>1678.2969969999999</v>
       </c>
       <c r="H60">
-        <v>1678.2969969999999</v>
+        <v>2.3050000000000001E-2</v>
       </c>
       <c r="I60">
-        <v>2.3050000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>98.323599999999999</v>
       </c>
       <c r="K60">
-        <v>98.323599999999999</v>
+        <v>100</v>
       </c>
       <c r="L60">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>0.34958299999999998</v>
       </c>
       <c r="N60">
-        <v>0.34958299999999998</v>
+        <v>12.454700000000001</v>
       </c>
       <c r="O60">
-        <v>12.454700000000001</v>
-      </c>
-      <c r="P60">
         <v>0.213501</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>195</v>
       </c>
-      <c r="B61">
-        <v>5</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="B61" t="s">
         <v>68</v>
       </c>
+      <c r="C61">
+        <v>77045</v>
+      </c>
       <c r="D61">
-        <v>77045</v>
+        <v>1330</v>
       </c>
       <c r="E61">
-        <v>1330</v>
+        <v>225.33537902055838</v>
       </c>
       <c r="F61">
-        <v>225.33537902055838</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G61">
-        <v>4.1470096879308791</v>
+        <v>1530.867</v>
       </c>
       <c r="H61">
-        <v>1530.867</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>90.051000000000002</v>
       </c>
       <c r="K61">
-        <v>90.051000000000002</v>
+        <v>0</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -4165,136 +3985,127 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="O61">
-        <v>428</v>
-      </c>
-      <c r="P61">
         <v>4.3502669999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>195</v>
       </c>
-      <c r="B62">
-        <v>5</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="B62" t="s">
         <v>69</v>
       </c>
+      <c r="C62">
+        <v>76004</v>
+      </c>
       <c r="D62">
-        <v>76004</v>
+        <v>710</v>
       </c>
       <c r="E62">
-        <v>710</v>
+        <v>185.96869752767057</v>
       </c>
       <c r="F62">
-        <v>185.96869752767057</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G62">
-        <v>4.1470096879308791</v>
+        <v>1335.275635</v>
       </c>
       <c r="H62">
-        <v>1335.275635</v>
+        <v>6.2576669999999996</v>
       </c>
       <c r="I62">
-        <v>6.2576669999999996</v>
+        <v>1.374814</v>
       </c>
       <c r="J62">
-        <v>1.374814</v>
+        <v>58.806429999999999</v>
       </c>
       <c r="K62">
-        <v>58.806429999999999</v>
+        <v>0</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>6.1195740000000001</v>
       </c>
       <c r="N62">
-        <v>6.1195740000000001</v>
+        <v>120.0887</v>
       </c>
       <c r="O62">
-        <v>120.0887</v>
-      </c>
-      <c r="P62">
         <v>1.5063949999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>195</v>
       </c>
-      <c r="B63">
-        <v>5</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B63" t="s">
         <v>70</v>
       </c>
+      <c r="C63">
+        <v>78016</v>
+      </c>
       <c r="D63">
-        <v>78016</v>
+        <v>556</v>
       </c>
       <c r="E63">
-        <v>556</v>
+        <v>515.40780131657789</v>
       </c>
       <c r="F63">
-        <v>515.40780131657789</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G63">
-        <v>4.1470096879308791</v>
+        <v>1382.72705</v>
       </c>
       <c r="H63">
-        <v>1382.72705</v>
+        <v>16.483789999999999</v>
       </c>
       <c r="I63">
-        <v>16.483789999999999</v>
+        <v>9.1783800000000006</v>
       </c>
       <c r="J63">
-        <v>9.1783800000000006</v>
+        <v>40.306379999999997</v>
       </c>
       <c r="K63">
-        <v>40.306379999999997</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.888957</v>
       </c>
       <c r="M63">
-        <v>1.888957</v>
+        <v>5.7970170000000003</v>
       </c>
       <c r="N63">
-        <v>5.7970170000000003</v>
+        <v>319.09609999999998</v>
       </c>
       <c r="O63">
-        <v>319.09609999999998</v>
-      </c>
-      <c r="P63">
         <v>1.813636</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>195</v>
       </c>
-      <c r="B64">
-        <v>5</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B64" t="s">
         <v>71</v>
       </c>
+      <c r="C64">
+        <v>65056</v>
+      </c>
       <c r="D64">
-        <v>65056</v>
+        <v>196.66666666666666</v>
       </c>
       <c r="E64">
-        <v>196.66666666666666</v>
+        <v>352.3239173551558</v>
       </c>
       <c r="F64">
-        <v>352.3239173551558</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G64">
-        <v>4.1470096879308791</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -4315,198 +4126,186 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>39943.199999999997</v>
       </c>
       <c r="O64">
-        <v>39943.199999999997</v>
-      </c>
-      <c r="P64">
         <v>0.146678</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>195</v>
       </c>
-      <c r="B65">
-        <v>13</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B65" t="s">
         <v>134</v>
       </c>
+      <c r="C65">
+        <v>71008</v>
+      </c>
       <c r="D65">
-        <v>71008</v>
+        <v>2505.6555555555556</v>
       </c>
       <c r="E65">
-        <v>2505.6555555555556</v>
+        <v>1277.3333333333333</v>
       </c>
       <c r="F65">
-        <v>1277.3333333333333</v>
+        <v>10</v>
       </c>
       <c r="G65">
-        <v>10</v>
+        <v>757.28666669999996</v>
       </c>
       <c r="H65">
-        <v>757.28666669999996</v>
+        <v>7.3332999999999995E-2</v>
       </c>
       <c r="I65">
-        <v>7.3332999999999995E-2</v>
+        <v>1.3383000000000001E-2</v>
       </c>
       <c r="J65">
-        <v>1.3383000000000001E-2</v>
+        <v>43.91133</v>
       </c>
       <c r="K65">
-        <v>43.91133</v>
+        <v>0</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>0.47533300000000001</v>
       </c>
       <c r="N65">
-        <v>0.47533300000000001</v>
+        <v>10052.41</v>
       </c>
       <c r="O65">
-        <v>10052.41</v>
-      </c>
-      <c r="P65">
         <v>3.0585800000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>195</v>
       </c>
-      <c r="B66">
-        <v>13</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B66" t="s">
         <v>135</v>
       </c>
+      <c r="C66">
+        <v>71003</v>
+      </c>
       <c r="D66">
-        <v>71003</v>
+        <v>2505.6555555555556</v>
       </c>
       <c r="E66">
-        <v>2505.6555555555556</v>
+        <v>1277.3333333333333</v>
       </c>
       <c r="F66">
-        <v>1277.3333333333333</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>10</v>
+        <v>187</v>
       </c>
       <c r="H66">
-        <v>187</v>
+        <v>1.06</v>
       </c>
       <c r="I66">
-        <v>1.06</v>
+        <v>0.11681900000000001</v>
       </c>
       <c r="J66">
-        <v>0.11681900000000001</v>
+        <v>9.01</v>
       </c>
       <c r="K66">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M66">
-        <v>3.64</v>
+        <v>1.61</v>
       </c>
       <c r="N66">
-        <v>1.61</v>
+        <v>488.6327</v>
       </c>
       <c r="O66">
-        <v>488.6327</v>
-      </c>
-      <c r="P66">
         <v>1.395524</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>195</v>
       </c>
-      <c r="B67">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B67" t="s">
         <v>136</v>
       </c>
+      <c r="C67">
+        <v>81004</v>
+      </c>
       <c r="D67">
-        <v>81004</v>
+        <v>2903</v>
       </c>
       <c r="E67">
-        <v>2903</v>
+        <v>1772</v>
       </c>
       <c r="F67">
-        <v>1772</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G67">
-        <v>10.397478991596639</v>
+        <v>90.323333739999995</v>
       </c>
       <c r="H67">
-        <v>90.323333739999995</v>
+        <v>0.26333299999999998</v>
       </c>
       <c r="I67">
-        <v>0.26333299999999998</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>2.0733329999999999</v>
       </c>
       <c r="K67">
-        <v>2.0733329999999999</v>
+        <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>0.55666700000000002</v>
       </c>
       <c r="M67">
-        <v>0.55666700000000002</v>
+        <v>2.6666669999999999</v>
       </c>
       <c r="N67">
-        <v>2.6666669999999999</v>
+        <v>32560</v>
       </c>
       <c r="O67">
-        <v>32560</v>
-      </c>
-      <c r="P67">
         <v>1.2489129999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>195</v>
       </c>
-      <c r="B68">
-        <v>13</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="B68" t="s">
         <v>137</v>
       </c>
+      <c r="C68">
+        <v>77056</v>
+      </c>
       <c r="D68">
-        <v>77056</v>
+        <v>443.4</v>
       </c>
       <c r="E68">
-        <v>443.4</v>
+        <v>1518.4430032697401</v>
       </c>
       <c r="F68">
-        <v>1518.4430032697401</v>
+        <v>9</v>
       </c>
       <c r="G68">
-        <v>9</v>
+        <v>102.3399963</v>
       </c>
       <c r="H68">
-        <v>102.3399963</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="K68">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -4515,395 +4314,371 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O68">
-        <v>5</v>
-      </c>
-      <c r="P68">
         <v>0.30094399999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>195</v>
       </c>
-      <c r="B69">
-        <v>13</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="B69" t="s">
         <v>138</v>
       </c>
+      <c r="C69">
+        <v>71105</v>
+      </c>
       <c r="D69">
-        <v>71105</v>
+        <v>443.4</v>
       </c>
       <c r="E69">
-        <v>443.4</v>
+        <v>1518.4430032697401</v>
       </c>
       <c r="F69">
-        <v>1518.4430032697401</v>
+        <v>9</v>
       </c>
       <c r="G69">
-        <v>9</v>
+        <v>564.82220459999996</v>
       </c>
       <c r="H69">
-        <v>564.82220459999996</v>
+        <v>4.4713339999999997</v>
       </c>
       <c r="I69">
-        <v>4.4713339999999997</v>
+        <v>3.4</v>
       </c>
       <c r="J69">
-        <v>3.4</v>
+        <v>8.1110000000000002E-3</v>
       </c>
       <c r="K69">
-        <v>8.1110000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>23.484999999999999</v>
       </c>
       <c r="N69">
-        <v>23.484999999999999</v>
+        <v>43.053330000000003</v>
       </c>
       <c r="O69">
-        <v>43.053330000000003</v>
-      </c>
-      <c r="P69">
         <v>2.2163439999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>195</v>
       </c>
-      <c r="B70">
-        <v>13</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B70" t="s">
         <v>139</v>
       </c>
+      <c r="C70">
+        <v>71041</v>
+      </c>
       <c r="D70">
-        <v>71041</v>
+        <v>594</v>
       </c>
       <c r="E70">
-        <v>594</v>
+        <v>1653.8799756971666</v>
       </c>
       <c r="F70">
-        <v>1653.8799756971666</v>
+        <v>8.4</v>
       </c>
       <c r="G70">
-        <v>8.4</v>
+        <v>555.80780030000005</v>
       </c>
       <c r="H70">
-        <v>555.80780030000005</v>
+        <v>5.4533329999999998</v>
       </c>
       <c r="I70">
-        <v>5.4533329999999998</v>
+        <v>2.75</v>
       </c>
       <c r="J70">
-        <v>2.75</v>
+        <v>1.3833329999999999</v>
       </c>
       <c r="K70">
-        <v>1.3833329999999999</v>
+        <v>0</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>19.442219999999999</v>
       </c>
       <c r="N70">
-        <v>19.442219999999999</v>
+        <v>49.23</v>
       </c>
       <c r="O70">
-        <v>49.23</v>
-      </c>
-      <c r="P70">
         <v>1.4048989999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>195</v>
       </c>
-      <c r="B71">
-        <v>13</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="B71" t="s">
         <v>140</v>
       </c>
+      <c r="C71">
+        <v>81013</v>
+      </c>
       <c r="D71">
-        <v>81013</v>
+        <v>2903</v>
       </c>
       <c r="E71">
-        <v>2903</v>
+        <v>1772</v>
       </c>
       <c r="F71">
-        <v>1772</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G71">
-        <v>10.397478991596639</v>
+        <v>900.70001219999995</v>
       </c>
       <c r="H71">
-        <v>900.70001219999995</v>
+        <v>15.2</v>
       </c>
       <c r="I71">
-        <v>15.2</v>
+        <v>3.3</v>
       </c>
       <c r="J71">
-        <v>3.3</v>
+        <v>0.46</v>
       </c>
       <c r="K71">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="N71">
-        <v>19.440000000000001</v>
+        <v>45.003329999999998</v>
       </c>
       <c r="O71">
-        <v>45.003329999999998</v>
-      </c>
-      <c r="P71">
         <v>0.95120400000000005</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
-      <c r="B72">
-        <v>13</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B72" t="s">
         <v>141</v>
       </c>
+      <c r="C72">
+        <v>81008</v>
+      </c>
       <c r="D72">
-        <v>81008</v>
+        <v>1368.2835566062515</v>
       </c>
       <c r="E72">
-        <v>1368.2835566062515</v>
+        <v>1730.2020304029807</v>
       </c>
       <c r="F72">
-        <v>1730.2020304029807</v>
+        <v>10.5</v>
       </c>
       <c r="G72">
-        <v>10.5</v>
+        <v>772.98309329999995</v>
       </c>
       <c r="H72">
-        <v>772.98309329999995</v>
+        <v>11.1219</v>
       </c>
       <c r="I72">
-        <v>11.1219</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J72">
-        <v>4.5999999999999996</v>
+        <v>1.501949</v>
       </c>
       <c r="K72">
-        <v>1.501949</v>
+        <v>0</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>19.761150000000001</v>
       </c>
       <c r="N72">
-        <v>19.761150000000001</v>
+        <v>74.308170000000004</v>
       </c>
       <c r="O72">
-        <v>74.308170000000004</v>
-      </c>
-      <c r="P72">
         <v>1.0949469999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>195</v>
       </c>
-      <c r="B73">
-        <v>13</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B73" t="s">
         <v>142</v>
       </c>
+      <c r="C73">
+        <v>71081</v>
+      </c>
       <c r="D73">
-        <v>71081</v>
+        <v>8180</v>
       </c>
       <c r="E73">
-        <v>8180</v>
+        <v>6261.6466104535029</v>
       </c>
       <c r="F73">
-        <v>6261.6466104535029</v>
+        <v>28.3</v>
       </c>
       <c r="G73">
-        <v>28.3</v>
+        <v>772.98309329999995</v>
       </c>
       <c r="H73">
-        <v>772.98309329999995</v>
+        <v>11.1219</v>
       </c>
       <c r="I73">
-        <v>11.1219</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J73">
-        <v>4.5999999999999996</v>
+        <v>1.501949</v>
       </c>
       <c r="K73">
-        <v>1.501949</v>
+        <v>0</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>19.761150000000001</v>
       </c>
       <c r="N73">
-        <v>19.761150000000001</v>
+        <v>74.308170000000004</v>
       </c>
       <c r="O73">
-        <v>74.308170000000004</v>
-      </c>
-      <c r="P73">
         <v>1.188402</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>195</v>
       </c>
-      <c r="B74">
-        <v>13</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="B74" t="s">
         <v>143</v>
       </c>
+      <c r="C74">
+        <v>71018</v>
+      </c>
       <c r="D74">
-        <v>71018</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="E74">
-        <v>1333.3333333333333</v>
+        <v>2704.2217653304615</v>
       </c>
       <c r="F74">
-        <v>2704.2217653304615</v>
+        <v>7.5284216775458965</v>
       </c>
       <c r="G74">
-        <v>7.5284216775458965</v>
+        <v>900.70001219999995</v>
       </c>
       <c r="H74">
-        <v>900.70001219999995</v>
+        <v>15.2</v>
       </c>
       <c r="I74">
-        <v>15.2</v>
+        <v>3.3</v>
       </c>
       <c r="J74">
-        <v>3.3</v>
+        <v>0.46</v>
       </c>
       <c r="K74">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="N74">
-        <v>19.440000000000001</v>
+        <v>45.003329999999998</v>
       </c>
       <c r="O74">
-        <v>45.003329999999998</v>
-      </c>
-      <c r="P74">
         <v>1.3253330000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>195</v>
       </c>
-      <c r="B75">
-        <v>13</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="B75" t="s">
         <v>144</v>
       </c>
+      <c r="C75">
+        <v>71039</v>
+      </c>
       <c r="D75">
-        <v>71039</v>
+        <v>1333.3333333333333</v>
       </c>
       <c r="E75">
-        <v>1333.3333333333333</v>
+        <v>2704.2217653304615</v>
       </c>
       <c r="F75">
-        <v>2704.2217653304615</v>
+        <v>7.5284216775458965</v>
       </c>
       <c r="G75">
-        <v>7.5284216775458965</v>
+        <v>772.98309329999995</v>
       </c>
       <c r="H75">
-        <v>772.98309329999995</v>
+        <v>11.1219</v>
       </c>
       <c r="I75">
-        <v>11.1219</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J75">
-        <v>4.5999999999999996</v>
+        <v>1.501949</v>
       </c>
       <c r="K75">
-        <v>1.501949</v>
+        <v>0</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>19.761150000000001</v>
       </c>
       <c r="N75">
-        <v>19.761150000000001</v>
+        <v>74.308170000000004</v>
       </c>
       <c r="O75">
-        <v>74.308170000000004</v>
-      </c>
-      <c r="P75">
         <v>0.94457400000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>195</v>
       </c>
-      <c r="B76">
-        <v>5</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="B76" t="s">
         <v>72</v>
       </c>
+      <c r="C76">
+        <v>72611</v>
+      </c>
       <c r="D76">
-        <v>72611</v>
+        <v>4452.4273529411776</v>
       </c>
       <c r="E76">
-        <v>4452.4273529411776</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>227.27172789833566</v>
       </c>
       <c r="G76">
-        <v>227.27172789833566</v>
+        <v>400.1698245</v>
       </c>
       <c r="H76">
-        <v>400.1698245</v>
+        <v>2.568924</v>
       </c>
       <c r="I76">
-        <v>2.568924</v>
+        <v>0.80778700000000003</v>
       </c>
       <c r="J76">
-        <v>0.80778700000000003</v>
+        <v>0</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -4912,48 +4687,45 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>17.94821</v>
       </c>
       <c r="N76">
-        <v>17.94821</v>
+        <v>83.454700000000003</v>
       </c>
       <c r="O76">
-        <v>83.454700000000003</v>
-      </c>
-      <c r="P76">
         <v>1.4687129999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>197</v>
       </c>
-      <c r="B77">
-        <v>6</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B77" t="s">
         <v>73</v>
       </c>
+      <c r="C77">
+        <v>84001</v>
+      </c>
       <c r="D77">
-        <v>84001</v>
+        <v>1853.3333333333333</v>
       </c>
       <c r="E77">
-        <v>1853.3333333333333</v>
+        <v>33495.408300043062</v>
       </c>
       <c r="F77">
-        <v>33495.408300043062</v>
+        <v>4.1470096879308791</v>
       </c>
       <c r="G77">
-        <v>4.1470096879308791</v>
+        <v>191</v>
       </c>
       <c r="H77">
-        <v>191</v>
+        <v>0.43</v>
       </c>
       <c r="I77">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="J77">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -4962,148 +4734,139 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>10.31</v>
       </c>
       <c r="N77">
-        <v>10.31</v>
+        <v>208.47309999999999</v>
       </c>
       <c r="O77">
-        <v>208.47309999999999</v>
-      </c>
-      <c r="P77">
         <v>2.0033099999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>197</v>
       </c>
-      <c r="B78">
-        <v>6</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="B78" t="s">
         <v>74</v>
       </c>
+      <c r="C78">
+        <v>79015</v>
+      </c>
       <c r="D78">
-        <v>79015</v>
+        <v>914.50476190476195</v>
       </c>
       <c r="E78">
-        <v>914.50476190476195</v>
+        <v>5594.2395753975461</v>
       </c>
       <c r="F78">
-        <v>5594.2395753975461</v>
+        <v>5.3898582166145301</v>
       </c>
       <c r="G78">
-        <v>5.3898582166145301</v>
+        <v>377.7900085</v>
       </c>
       <c r="H78">
-        <v>377.7900085</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="I78">
-        <v>0.38500000000000001</v>
+        <v>0.182033</v>
       </c>
       <c r="J78">
-        <v>0.182033</v>
+        <v>8.0850000000000009</v>
       </c>
       <c r="K78">
-        <v>8.0850000000000009</v>
+        <v>0</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="N78">
-        <v>13.3</v>
+        <v>243</v>
       </c>
       <c r="O78">
-        <v>243</v>
-      </c>
-      <c r="P78">
         <v>1.550664</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>197</v>
       </c>
-      <c r="B79">
-        <v>6</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="B79" t="s">
         <v>75</v>
       </c>
+      <c r="C79">
+        <v>79016</v>
+      </c>
       <c r="D79">
-        <v>79016</v>
+        <v>210.34444444444443</v>
       </c>
       <c r="E79">
-        <v>210.34444444444443</v>
+        <v>3263.5062840917908</v>
       </c>
       <c r="F79">
-        <v>3263.5062840917908</v>
+        <v>5.3898582166145301</v>
       </c>
       <c r="G79">
-        <v>5.3898582166145301</v>
+        <v>393.13766479999998</v>
       </c>
       <c r="H79">
-        <v>393.13766479999998</v>
+        <v>2.3029999999999999</v>
       </c>
       <c r="I79">
-        <v>2.3029999999999999</v>
+        <v>0.79250299999999996</v>
       </c>
       <c r="J79">
-        <v>0.79250299999999996</v>
+        <v>1.333E-3</v>
       </c>
       <c r="K79">
-        <v>1.333E-3</v>
+        <v>0</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>18.111999999999998</v>
       </c>
       <c r="N79">
-        <v>18.111999999999998</v>
+        <v>52</v>
       </c>
       <c r="O79">
-        <v>52</v>
-      </c>
-      <c r="P79">
         <v>1.7219089999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>197</v>
       </c>
-      <c r="B80">
-        <v>6</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B80" t="s">
         <v>76</v>
       </c>
+      <c r="C80">
+        <v>84032</v>
+      </c>
       <c r="D80">
-        <v>84032</v>
+        <v>3320.9089509884666</v>
       </c>
       <c r="E80">
-        <v>3320.9089509884666</v>
+        <v>4474.4591510944665</v>
       </c>
       <c r="F80">
-        <v>4474.4591510944665</v>
+        <v>26.5</v>
       </c>
       <c r="G80">
-        <v>26.5</v>
+        <v>538.27001949999999</v>
       </c>
       <c r="H80">
-        <v>538.27001949999999</v>
+        <v>1.32</v>
       </c>
       <c r="I80">
-        <v>1.32</v>
+        <v>0.6</v>
       </c>
       <c r="J80">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -5112,648 +4875,609 @@
         <v>0</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>28.79</v>
       </c>
       <c r="N80">
-        <v>28.79</v>
+        <v>13585.06</v>
       </c>
       <c r="O80">
-        <v>13585.06</v>
-      </c>
-      <c r="P80">
         <v>1.9439139999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>77</v>
       </c>
-      <c r="B81">
-        <v>7</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B81" t="s">
         <v>78</v>
       </c>
+      <c r="C81">
+        <v>79086</v>
+      </c>
       <c r="D81">
-        <v>79086</v>
+        <v>3500</v>
       </c>
       <c r="E81">
-        <v>3500</v>
+        <v>12800</v>
       </c>
       <c r="F81">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G81">
-        <v>52</v>
+        <v>422.07983330000002</v>
       </c>
       <c r="H81">
-        <v>422.07983330000002</v>
+        <v>1.2227220000000001</v>
       </c>
       <c r="I81">
-        <v>1.2227220000000001</v>
+        <v>0.30794700000000003</v>
       </c>
       <c r="J81">
-        <v>0.30794700000000003</v>
+        <v>20.403230000000001</v>
       </c>
       <c r="K81">
-        <v>20.403230000000001</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>4.7522219999999997</v>
       </c>
       <c r="M81">
-        <v>4.7522219999999997</v>
+        <v>4.2796589999999997</v>
       </c>
       <c r="N81">
-        <v>4.2796589999999997</v>
+        <v>342.63990000000001</v>
       </c>
       <c r="O81">
-        <v>342.63990000000001</v>
-      </c>
-      <c r="P81">
         <v>1.004148</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>77</v>
       </c>
-      <c r="B82">
-        <v>7</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" t="s">
         <v>79</v>
       </c>
+      <c r="C82">
+        <v>80023</v>
+      </c>
       <c r="D82">
-        <v>80023</v>
+        <v>4005.4397586713299</v>
       </c>
       <c r="E82">
-        <v>4005.4397586713299</v>
+        <v>7509.0702772841823</v>
       </c>
       <c r="F82">
-        <v>7509.0702772841823</v>
+        <v>34.875</v>
       </c>
       <c r="G82">
-        <v>34.875</v>
+        <v>1471.4300539999999</v>
       </c>
       <c r="H82">
-        <v>1471.4300539999999</v>
+        <v>5.2966670000000002</v>
       </c>
       <c r="I82">
-        <v>5.2966670000000002</v>
+        <v>1.6020179999999999</v>
       </c>
       <c r="J82">
-        <v>1.6020179999999999</v>
+        <v>63.378329999999998</v>
       </c>
       <c r="K82">
-        <v>63.378329999999998</v>
+        <v>0</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>11.64833</v>
       </c>
       <c r="N82">
-        <v>11.64833</v>
+        <v>3644.788</v>
       </c>
       <c r="O82">
-        <v>3644.788</v>
-      </c>
-      <c r="P82">
         <v>2.6550150000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>77</v>
       </c>
-      <c r="B83">
-        <v>7</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B83" t="s">
         <v>80</v>
       </c>
+      <c r="C83">
+        <v>80022</v>
+      </c>
       <c r="D83">
-        <v>80022</v>
+        <v>2857.8571428571427</v>
       </c>
       <c r="E83">
-        <v>2857.8571428571427</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>208.95434557966715</v>
       </c>
       <c r="G83">
-        <v>208.95434557966715</v>
+        <v>700.84111110000003</v>
       </c>
       <c r="H83">
-        <v>700.84111110000003</v>
+        <v>6.6322219999999996</v>
       </c>
       <c r="I83">
-        <v>6.6322219999999996</v>
+        <v>1.105985</v>
       </c>
       <c r="J83">
-        <v>1.105985</v>
+        <v>1.4619439999999999</v>
       </c>
       <c r="K83">
-        <v>1.4619439999999999</v>
+        <v>0</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>25.329170000000001</v>
       </c>
       <c r="N83">
-        <v>25.329170000000001</v>
+        <v>355.71969999999999</v>
       </c>
       <c r="O83">
-        <v>355.71969999999999</v>
-      </c>
-      <c r="P83">
         <v>1.323229</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>77</v>
       </c>
-      <c r="B84">
-        <v>7</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="B84" t="s">
         <v>81</v>
       </c>
+      <c r="C84">
+        <v>80101</v>
+      </c>
       <c r="D84">
-        <v>80101</v>
+        <v>14550</v>
       </c>
       <c r="E84">
-        <v>14550</v>
+        <v>12800</v>
       </c>
       <c r="F84">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G84">
-        <v>52</v>
+        <v>404.93</v>
       </c>
       <c r="H84">
-        <v>404.93</v>
+        <v>5.53</v>
       </c>
       <c r="I84">
-        <v>5.53</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="J84">
-        <v>2.1850000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="K84">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M84">
-        <v>0.9</v>
+        <v>4.41</v>
       </c>
       <c r="N84">
-        <v>4.41</v>
+        <v>388</v>
       </c>
       <c r="O84">
-        <v>388</v>
-      </c>
-      <c r="P84">
         <v>1.4571430000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>77</v>
       </c>
-      <c r="B85">
-        <v>7</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="B85" t="s">
         <v>82</v>
       </c>
+      <c r="C85">
+        <v>80025</v>
+      </c>
       <c r="D85">
-        <v>80025</v>
+        <v>4226.965144927537</v>
       </c>
       <c r="E85">
-        <v>4226.965144927537</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>208.95434557966715</v>
       </c>
       <c r="G85">
-        <v>208.95434557966715</v>
+        <v>635.28778079999995</v>
       </c>
       <c r="H85">
-        <v>635.28778079999995</v>
+        <v>8.2094740000000002</v>
       </c>
       <c r="I85">
-        <v>8.2094740000000002</v>
+        <v>3.1555550000000001</v>
       </c>
       <c r="J85">
-        <v>3.1555550000000001</v>
+        <v>0.80679599999999996</v>
       </c>
       <c r="K85">
-        <v>0.80679599999999996</v>
+        <v>0</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>18.695399999999999</v>
       </c>
       <c r="N85">
-        <v>18.695399999999999</v>
+        <v>76.880740000000003</v>
       </c>
       <c r="O85">
-        <v>76.880740000000003</v>
-      </c>
-      <c r="P85">
         <v>0.88880000000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>77</v>
       </c>
-      <c r="B86">
-        <v>7</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="B86" t="s">
         <v>83</v>
       </c>
+      <c r="C86">
+        <v>69009</v>
+      </c>
       <c r="D86">
-        <v>69009</v>
+        <v>3320.9089509884666</v>
       </c>
       <c r="E86">
-        <v>3320.9089509884666</v>
+        <v>4474.4591510944665</v>
       </c>
       <c r="F86">
-        <v>4474.4591510944665</v>
+        <v>26.5</v>
       </c>
       <c r="G86">
-        <v>26.5</v>
+        <v>373.88000490000002</v>
       </c>
       <c r="H86">
-        <v>373.88000490000002</v>
+        <v>1.83</v>
       </c>
       <c r="I86">
-        <v>1.83</v>
+        <v>0.4</v>
       </c>
       <c r="J86">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="K86">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="N86">
-        <v>17.98</v>
+        <v>710.68299999999999</v>
       </c>
       <c r="O86">
-        <v>710.68299999999999</v>
-      </c>
-      <c r="P86">
         <v>1.0522480000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>77</v>
       </c>
-      <c r="B87">
-        <v>7</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="B87" t="s">
         <v>84</v>
       </c>
+      <c r="C87">
+        <v>82128</v>
+      </c>
       <c r="D87">
-        <v>82128</v>
+        <v>2400</v>
       </c>
       <c r="E87">
-        <v>2400</v>
+        <v>2256.485722150212</v>
       </c>
       <c r="F87">
-        <v>2256.485722150212</v>
+        <v>7.5284216775458965</v>
       </c>
       <c r="G87">
-        <v>7.5284216775458965</v>
+        <v>562.79553220000003</v>
       </c>
       <c r="H87">
-        <v>562.79553220000003</v>
+        <v>9.0449999999999999</v>
       </c>
       <c r="I87">
-        <v>9.0449999999999999</v>
+        <v>2.6423589999999999</v>
       </c>
       <c r="J87">
-        <v>2.6423589999999999</v>
+        <v>2.1327780000000001</v>
       </c>
       <c r="K87">
-        <v>2.1327780000000001</v>
+        <v>0</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>11.286670000000001</v>
       </c>
       <c r="N87">
-        <v>11.286670000000001</v>
+        <v>160.71879999999999</v>
       </c>
       <c r="O87">
-        <v>160.71879999999999</v>
-      </c>
-      <c r="P87">
         <v>0.87119899999999995</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>77</v>
       </c>
-      <c r="B88">
-        <v>7</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="B88" t="s">
         <v>85</v>
       </c>
+      <c r="C88">
+        <v>69006</v>
+      </c>
       <c r="D88">
-        <v>69006</v>
+        <v>4226.965144927537</v>
       </c>
       <c r="E88">
-        <v>4226.965144927537</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>208.95434557966715</v>
       </c>
       <c r="G88">
-        <v>208.95434557966715</v>
+        <v>2082</v>
       </c>
       <c r="H88">
-        <v>2082</v>
+        <v>26.425830000000001</v>
       </c>
       <c r="I88">
-        <v>26.425830000000001</v>
+        <v>16.0107</v>
       </c>
       <c r="J88">
-        <v>16.0107</v>
+        <v>38.950000000000003</v>
       </c>
       <c r="K88">
-        <v>38.950000000000003</v>
+        <v>0</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>25.99</v>
       </c>
       <c r="N88">
-        <v>25.99</v>
+        <v>321.93279999999999</v>
       </c>
       <c r="O88">
-        <v>321.93279999999999</v>
-      </c>
-      <c r="P88">
         <v>1.95021</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>77</v>
       </c>
-      <c r="B89">
-        <v>7</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="B89" t="s">
         <v>86</v>
       </c>
+      <c r="C89">
+        <v>69077</v>
+      </c>
       <c r="D89">
-        <v>69077</v>
+        <v>26937.633264372518</v>
       </c>
       <c r="E89">
-        <v>26937.633264372518</v>
+        <v>18136.156896200948</v>
       </c>
       <c r="F89">
-        <v>18136.156896200948</v>
+        <v>112.26701297421286</v>
       </c>
       <c r="G89">
-        <v>112.26701297421286</v>
+        <v>1348.713379</v>
       </c>
       <c r="H89">
-        <v>1348.713379</v>
+        <v>6.74</v>
       </c>
       <c r="I89">
-        <v>6.74</v>
+        <v>4.2</v>
       </c>
       <c r="J89">
-        <v>4.2</v>
+        <v>56.996670000000002</v>
       </c>
       <c r="K89">
-        <v>56.996670000000002</v>
+        <v>0</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="N89">
-        <v>7.67</v>
+        <v>93.803340000000006</v>
       </c>
       <c r="O89">
-        <v>93.803340000000006</v>
-      </c>
-      <c r="P89">
         <v>0.888486</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>77</v>
       </c>
-      <c r="B90">
-        <v>7</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="B90" t="s">
         <v>87</v>
       </c>
+      <c r="C90">
+        <v>81083</v>
+      </c>
       <c r="D90">
-        <v>81083</v>
+        <v>26937.633264372518</v>
       </c>
       <c r="E90">
-        <v>26937.633264372518</v>
+        <v>18136.156896200948</v>
       </c>
       <c r="F90">
-        <v>18136.156896200948</v>
+        <v>112.26701297421286</v>
       </c>
       <c r="G90">
-        <v>112.26701297421286</v>
+        <v>982.2150269</v>
       </c>
       <c r="H90">
-        <v>982.2150269</v>
+        <v>23.73967</v>
       </c>
       <c r="I90">
-        <v>23.73967</v>
+        <v>11.82</v>
       </c>
       <c r="J90">
-        <v>11.82</v>
+        <v>4.154763</v>
       </c>
       <c r="K90">
-        <v>4.154763</v>
+        <v>0</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>1.9539029999999999</v>
       </c>
       <c r="N90">
-        <v>1.9539029999999999</v>
+        <v>51.723999999999997</v>
       </c>
       <c r="O90">
-        <v>51.723999999999997</v>
-      </c>
-      <c r="P90">
         <v>1.0493650000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>77</v>
       </c>
-      <c r="B91">
-        <v>7</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="B91" t="s">
         <v>88</v>
       </c>
+      <c r="C91">
+        <v>65041</v>
+      </c>
       <c r="D91">
-        <v>65041</v>
+        <v>2925</v>
       </c>
       <c r="E91">
-        <v>2925</v>
+        <v>1388.8273394164951</v>
       </c>
       <c r="F91">
-        <v>1388.8273394164951</v>
+        <v>79.706150270978782</v>
       </c>
       <c r="G91">
-        <v>79.706150270978782</v>
+        <v>316.89868159999997</v>
       </c>
       <c r="H91">
-        <v>316.89868159999997</v>
+        <v>2.1691669999999998</v>
       </c>
       <c r="I91">
-        <v>2.1691669999999998</v>
+        <v>1.4</v>
       </c>
       <c r="J91">
-        <v>1.4</v>
+        <v>10.9215</v>
       </c>
       <c r="K91">
-        <v>10.9215</v>
+        <v>0</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>0.23333300000000001</v>
       </c>
       <c r="M91">
-        <v>0.23333300000000001</v>
+        <v>3.1219999999999999</v>
       </c>
       <c r="N91">
-        <v>3.1219999999999999</v>
+        <v>55.70167</v>
       </c>
       <c r="O91">
-        <v>55.70167</v>
-      </c>
-      <c r="P91">
         <v>0.89267799999999997</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>77</v>
       </c>
-      <c r="B92">
-        <v>7</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B92" t="s">
         <v>89</v>
       </c>
+      <c r="C92">
+        <v>81031</v>
+      </c>
       <c r="D92">
-        <v>81031</v>
+        <v>5300</v>
       </c>
       <c r="E92">
-        <v>5300</v>
+        <v>12800</v>
       </c>
       <c r="F92">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G92">
-        <v>52</v>
+        <v>2768.2861330000001</v>
       </c>
       <c r="H92">
-        <v>2768.2861330000001</v>
+        <v>74.40258</v>
       </c>
       <c r="I92">
-        <v>74.40258</v>
+        <v>44.933329999999998</v>
       </c>
       <c r="J92">
-        <v>44.933329999999998</v>
+        <v>0.51776800000000001</v>
       </c>
       <c r="K92">
-        <v>0.51776800000000001</v>
+        <v>0</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>0.38756499999999999</v>
       </c>
       <c r="N92">
-        <v>0.38756499999999999</v>
+        <v>324.18110000000001</v>
       </c>
       <c r="O92">
-        <v>324.18110000000001</v>
-      </c>
-      <c r="P92">
         <v>2.365434</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>77</v>
       </c>
-      <c r="B93">
-        <v>7</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="B93" t="s">
         <v>90</v>
       </c>
+      <c r="C93">
+        <v>79012</v>
+      </c>
       <c r="D93">
-        <v>79012</v>
+        <v>5300</v>
       </c>
       <c r="E93">
-        <v>5300</v>
+        <v>12800</v>
       </c>
       <c r="F93">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G93">
-        <v>52</v>
+        <v>2632.1840820000002</v>
       </c>
       <c r="H93">
-        <v>2632.1840820000002</v>
+        <v>71.140110000000007</v>
       </c>
       <c r="I93">
-        <v>71.140110000000007</v>
+        <v>19.233329999999999</v>
       </c>
       <c r="J93">
-        <v>19.233329999999999</v>
+        <v>0</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -5765,677 +5489,635 @@
         <v>0</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>813.18430000000001</v>
       </c>
       <c r="O93">
-        <v>813.18430000000001</v>
-      </c>
-      <c r="P93">
         <v>0.86329100000000003</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>77</v>
       </c>
-      <c r="B94">
-        <v>7</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="B94" t="s">
         <v>91</v>
       </c>
+      <c r="C94">
+        <v>79031</v>
+      </c>
       <c r="D94">
-        <v>79031</v>
+        <v>2925</v>
       </c>
       <c r="E94">
-        <v>2925</v>
+        <v>1388.8273394164951</v>
       </c>
       <c r="F94">
-        <v>1388.8273394164951</v>
+        <v>79.706150270978782</v>
       </c>
       <c r="G94">
-        <v>79.706150270978782</v>
+        <v>1280.644775</v>
       </c>
       <c r="H94">
-        <v>1280.644775</v>
+        <v>27.90767</v>
       </c>
       <c r="I94">
-        <v>27.90767</v>
+        <v>16.173739999999999</v>
       </c>
       <c r="J94">
-        <v>16.173739999999999</v>
+        <v>4.1181660000000004</v>
       </c>
       <c r="K94">
-        <v>4.1181660000000004</v>
+        <v>0</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>10.47367</v>
       </c>
       <c r="N94">
-        <v>10.47367</v>
+        <v>786.25909999999999</v>
       </c>
       <c r="O94">
-        <v>786.25909999999999</v>
-      </c>
-      <c r="P94">
         <v>5.4400969999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>77</v>
       </c>
-      <c r="B95">
-        <v>7</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="B95" t="s">
         <v>92</v>
       </c>
+      <c r="C95">
+        <v>79009</v>
+      </c>
       <c r="D95">
-        <v>79009</v>
+        <v>5300</v>
       </c>
       <c r="E95">
-        <v>5300</v>
+        <v>12800</v>
       </c>
       <c r="F95">
-        <v>12800</v>
+        <v>52</v>
       </c>
       <c r="G95">
-        <v>52</v>
+        <v>1280.644775</v>
       </c>
       <c r="H95">
-        <v>1280.644775</v>
+        <v>27.90767</v>
       </c>
       <c r="I95">
-        <v>27.90767</v>
+        <v>15.9</v>
       </c>
       <c r="J95">
-        <v>15.9</v>
+        <v>4.1181660000000004</v>
       </c>
       <c r="K95">
-        <v>4.1181660000000004</v>
+        <v>0</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>10.47367</v>
       </c>
       <c r="N95">
-        <v>10.47367</v>
+        <v>780.42600000000004</v>
       </c>
       <c r="O95">
-        <v>780.42600000000004</v>
-      </c>
-      <c r="P95">
         <v>2.3193579999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
-      <c r="B96">
-        <v>7</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="B96" t="s">
         <v>93</v>
       </c>
+      <c r="C96">
+        <v>81022</v>
+      </c>
       <c r="D96">
-        <v>81022</v>
+        <v>13999.971734892786</v>
       </c>
       <c r="E96">
-        <v>13999.971734892786</v>
+        <v>7594.0380444357997</v>
       </c>
       <c r="F96">
-        <v>7594.0380444357997</v>
+        <v>76</v>
       </c>
       <c r="G96">
-        <v>76</v>
+        <v>359.10000609999997</v>
       </c>
       <c r="H96">
-        <v>359.10000609999997</v>
+        <v>2.4</v>
       </c>
       <c r="I96">
-        <v>2.4</v>
+        <v>1.2171510000000001</v>
       </c>
       <c r="J96">
-        <v>1.2171510000000001</v>
+        <v>13.9</v>
       </c>
       <c r="K96">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="O96">
-        <v>65</v>
-      </c>
-      <c r="P96">
         <v>0.58797299999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>77</v>
       </c>
-      <c r="B97">
-        <v>7</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="B97" t="s">
         <v>94</v>
       </c>
+      <c r="C97">
+        <v>65026</v>
+      </c>
       <c r="D97">
-        <v>65026</v>
+        <v>26937.633264372518</v>
       </c>
       <c r="E97">
-        <v>26937.633264372518</v>
+        <v>18136.156896200948</v>
       </c>
       <c r="F97">
-        <v>18136.156896200948</v>
+        <v>112.26701297421286</v>
       </c>
       <c r="G97">
-        <v>112.26701297421286</v>
+        <v>982.2150269</v>
       </c>
       <c r="H97">
-        <v>982.2150269</v>
+        <v>23.73967</v>
       </c>
       <c r="I97">
-        <v>23.73967</v>
+        <v>11.82</v>
       </c>
       <c r="J97">
-        <v>11.82</v>
+        <v>4.154763</v>
       </c>
       <c r="K97">
-        <v>4.154763</v>
+        <v>0</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>1.9539029999999999</v>
       </c>
       <c r="N97">
-        <v>1.9539029999999999</v>
+        <v>51.723999999999997</v>
       </c>
       <c r="O97">
-        <v>51.723999999999997</v>
-      </c>
-      <c r="P97">
         <v>1.5617259999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>77</v>
       </c>
-      <c r="B98">
-        <v>7</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B98" t="s">
         <v>95</v>
       </c>
+      <c r="C98">
+        <v>65028</v>
+      </c>
       <c r="D98">
-        <v>65028</v>
+        <v>3983.450752638113</v>
       </c>
       <c r="E98">
-        <v>3983.450752638113</v>
+        <v>7509.0702772841823</v>
       </c>
       <c r="F98">
-        <v>7509.0702772841823</v>
+        <v>34.875</v>
       </c>
       <c r="G98">
-        <v>34.875</v>
+        <v>233</v>
       </c>
       <c r="H98">
-        <v>233</v>
+        <v>1.81</v>
       </c>
       <c r="I98">
-        <v>1.81</v>
+        <v>1.149076</v>
       </c>
       <c r="J98">
-        <v>1.149076</v>
+        <v>6.51</v>
       </c>
       <c r="K98">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N98">
-        <v>3.23</v>
+        <v>61.640329999999999</v>
       </c>
       <c r="O98">
-        <v>61.640329999999999</v>
-      </c>
-      <c r="P98">
         <v>0.22814999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>77</v>
       </c>
-      <c r="B99">
-        <v>7</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="B99" t="s">
         <v>96</v>
       </c>
+      <c r="C99">
+        <v>63036</v>
+      </c>
       <c r="D99">
-        <v>63036</v>
+        <v>794.44444444444446</v>
       </c>
       <c r="E99">
-        <v>794.44444444444446</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F99">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G99">
-        <v>57.5</v>
+        <v>203.7206726</v>
       </c>
       <c r="H99">
-        <v>203.7206726</v>
+        <v>0.41783300000000001</v>
       </c>
       <c r="I99">
-        <v>0.41783300000000001</v>
+        <v>0.26473099999999999</v>
       </c>
       <c r="J99">
-        <v>0.26473099999999999</v>
+        <v>7.0369770000000003</v>
       </c>
       <c r="K99">
-        <v>7.0369770000000003</v>
+        <v>0</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>4.0371899999999998</v>
       </c>
       <c r="N99">
-        <v>4.0371899999999998</v>
+        <v>68.898989999999998</v>
       </c>
       <c r="O99">
-        <v>68.898989999999998</v>
-      </c>
-      <c r="P99">
         <v>1.508699</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>77</v>
       </c>
-      <c r="B100">
-        <v>7</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="B100" t="s">
         <v>97</v>
       </c>
+      <c r="C100">
+        <v>65048</v>
+      </c>
       <c r="D100">
-        <v>65048</v>
+        <v>2004.06878364198</v>
       </c>
       <c r="E100">
-        <v>2004.06878364198</v>
+        <v>1647.2967035570932</v>
       </c>
       <c r="F100">
-        <v>1647.2967035570932</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G100">
-        <v>10.397478991596639</v>
+        <v>755.09997559999999</v>
       </c>
       <c r="H100">
-        <v>755.09997559999999</v>
+        <v>13.7</v>
       </c>
       <c r="I100">
-        <v>13.7</v>
+        <v>8.0069110000000006</v>
       </c>
       <c r="J100">
-        <v>8.0069110000000006</v>
+        <v>1.6</v>
       </c>
       <c r="K100">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N100">
-        <v>13</v>
+        <v>475.6687</v>
       </c>
       <c r="O100">
-        <v>475.6687</v>
-      </c>
-      <c r="P100">
         <v>2.6442570000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>77</v>
       </c>
-      <c r="B101">
-        <v>7</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" t="s">
         <v>98</v>
       </c>
+      <c r="C101">
+        <v>65021</v>
+      </c>
       <c r="D101">
-        <v>65021</v>
+        <v>260</v>
       </c>
       <c r="E101">
-        <v>260</v>
+        <v>450</v>
       </c>
       <c r="F101">
-        <v>450</v>
+        <v>2</v>
       </c>
       <c r="G101">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="H101">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="I101">
         <v>0</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="K101">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N101">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
         <v>0.64951599999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>77</v>
       </c>
-      <c r="B102">
-        <v>7</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" t="s">
         <v>99</v>
       </c>
+      <c r="C102">
+        <v>80066</v>
+      </c>
       <c r="D102">
-        <v>80066</v>
+        <v>2004.06878364198</v>
       </c>
       <c r="E102">
-        <v>2004.06878364198</v>
+        <v>1647.2967035570932</v>
       </c>
       <c r="F102">
-        <v>1647.2967035570932</v>
+        <v>10.397478991596639</v>
       </c>
       <c r="G102">
-        <v>10.397478991596639</v>
+        <v>270.0400085</v>
       </c>
       <c r="H102">
-        <v>270.0400085</v>
+        <v>3.234</v>
       </c>
       <c r="I102">
-        <v>3.234</v>
+        <v>2.0128560000000002</v>
       </c>
       <c r="J102">
-        <v>2.0128560000000002</v>
+        <v>5.9160000000000004</v>
       </c>
       <c r="K102">
-        <v>5.9160000000000004</v>
+        <v>0</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N102">
-        <v>2.93</v>
+        <v>63.76</v>
       </c>
       <c r="O102">
-        <v>63.76</v>
-      </c>
-      <c r="P102">
         <v>0.23026199999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>77</v>
       </c>
-      <c r="B103">
-        <v>7</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" t="s">
         <v>100</v>
       </c>
+      <c r="C103">
+        <v>81029</v>
+      </c>
       <c r="D103">
-        <v>81029</v>
+        <v>1600</v>
       </c>
       <c r="E103">
-        <v>1600</v>
+        <v>1247.109290423776</v>
       </c>
       <c r="F103">
-        <v>1247.109290423776</v>
+        <v>5.52</v>
       </c>
       <c r="G103">
-        <v>5.52</v>
+        <v>1269.877808</v>
       </c>
       <c r="H103">
-        <v>1269.877808</v>
+        <v>2.121111</v>
       </c>
       <c r="I103">
-        <v>2.121111</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="J103">
-        <v>0.68400000000000005</v>
+        <v>61.635480000000001</v>
       </c>
       <c r="K103">
-        <v>61.635480000000001</v>
+        <v>0</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>2.608889</v>
       </c>
       <c r="M103">
-        <v>2.608889</v>
+        <v>9.8278549999999996</v>
       </c>
       <c r="N103">
-        <v>9.8278549999999996</v>
+        <v>681.9</v>
       </c>
       <c r="O103">
-        <v>681.9</v>
-      </c>
-      <c r="P103">
         <v>0.78464</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>77</v>
       </c>
-      <c r="B104">
-        <v>7</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="B104" t="s">
         <v>101</v>
       </c>
+      <c r="C104">
+        <v>79028</v>
+      </c>
       <c r="D104">
-        <v>79028</v>
+        <v>44570</v>
       </c>
       <c r="E104">
-        <v>44570</v>
+        <v>17481</v>
       </c>
       <c r="F104">
-        <v>17481</v>
+        <v>33.5</v>
       </c>
       <c r="G104">
-        <v>33.5</v>
+        <v>1846.2479249999999</v>
       </c>
       <c r="H104">
-        <v>1846.2479249999999</v>
+        <v>13.67667</v>
       </c>
       <c r="I104">
-        <v>13.67667</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J104">
-        <v>4.4000000000000004</v>
+        <v>69.648110000000003</v>
       </c>
       <c r="K104">
-        <v>69.648110000000003</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>3.17625</v>
       </c>
       <c r="M104">
-        <v>3.17625</v>
+        <v>10.869389999999999</v>
       </c>
       <c r="N104">
-        <v>10.869389999999999</v>
+        <v>854.35670000000005</v>
       </c>
       <c r="O104">
-        <v>854.35670000000005</v>
-      </c>
-      <c r="P104">
         <v>1.1999070000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>77</v>
       </c>
-      <c r="B105">
-        <v>7</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="B105" t="s">
         <v>102</v>
       </c>
+      <c r="C105">
+        <v>79065</v>
+      </c>
       <c r="D105">
-        <v>79065</v>
+        <v>1997.5</v>
       </c>
       <c r="E105">
-        <v>1997.5</v>
+        <v>3977.5725722325878</v>
       </c>
       <c r="F105">
-        <v>3977.5725722325878</v>
+        <v>9</v>
       </c>
       <c r="G105">
-        <v>9</v>
+        <v>1834.223389</v>
       </c>
       <c r="H105">
-        <v>1834.223389</v>
+        <v>11.338889999999999</v>
       </c>
       <c r="I105">
-        <v>11.338889999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J105">
-        <v>3.9</v>
+        <v>76.278049999999993</v>
       </c>
       <c r="K105">
-        <v>76.278049999999993</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>2.7366670000000002</v>
       </c>
       <c r="M105">
-        <v>2.7366670000000002</v>
+        <v>8.3875069999999994</v>
       </c>
       <c r="N105">
-        <v>8.3875069999999994</v>
+        <v>352.02670000000001</v>
       </c>
       <c r="O105">
-        <v>352.02670000000001</v>
-      </c>
-      <c r="P105">
         <v>1.1519680000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>77</v>
       </c>
-      <c r="B106">
-        <v>7</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="B106" t="s">
         <v>103</v>
       </c>
+      <c r="C106">
+        <v>80059</v>
+      </c>
       <c r="D106">
-        <v>80059</v>
+        <v>1560</v>
       </c>
       <c r="E106">
-        <v>1560</v>
+        <v>431.86296717861296</v>
       </c>
       <c r="F106">
-        <v>431.86296717861296</v>
+        <v>33.5</v>
       </c>
       <c r="G106">
-        <v>33.5</v>
+        <v>1756.4766850000001</v>
       </c>
       <c r="H106">
-        <v>1756.4766850000001</v>
+        <v>19.510000000000002</v>
       </c>
       <c r="I106">
-        <v>19.510000000000002</v>
+        <v>5.9815969999999998</v>
       </c>
       <c r="J106">
-        <v>5.9815969999999998</v>
+        <v>54.416670000000003</v>
       </c>
       <c r="K106">
-        <v>54.416670000000003</v>
+        <v>0</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>8.3333000000000004E-2</v>
       </c>
       <c r="M106">
-        <v>8.3333000000000004E-2</v>
+        <v>6.4866669999999997</v>
       </c>
       <c r="N106">
-        <v>6.4866669999999997</v>
+        <v>331.93200000000002</v>
       </c>
       <c r="O106">
-        <v>331.93200000000002</v>
-      </c>
-      <c r="P106">
         <v>1.749007</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>77</v>
       </c>
-      <c r="B107">
-        <v>7</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B107" t="s">
         <v>104</v>
       </c>
+      <c r="C107">
+        <v>81021</v>
+      </c>
       <c r="D107">
-        <v>81021</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6444,216 +6126,204 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="H107">
-        <v>969</v>
+        <v>12.59</v>
       </c>
       <c r="I107">
-        <v>12.59</v>
+        <v>5.09</v>
       </c>
       <c r="J107">
-        <v>5.09</v>
+        <v>16.73</v>
       </c>
       <c r="K107">
-        <v>16.73</v>
+        <v>0</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M107">
-        <v>0.51</v>
+        <v>13.11</v>
       </c>
       <c r="N107">
-        <v>13.11</v>
+        <v>948.08</v>
       </c>
       <c r="O107">
-        <v>948.08</v>
-      </c>
-      <c r="P107">
         <v>3.250232</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>77</v>
       </c>
-      <c r="B108">
-        <v>7</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="B108" t="s">
         <v>105</v>
       </c>
+      <c r="C108">
+        <v>69127</v>
+      </c>
       <c r="D108">
-        <v>69127</v>
+        <v>1935.6666666666665</v>
       </c>
       <c r="E108">
-        <v>1935.6666666666665</v>
+        <v>6848.7837130653252</v>
       </c>
       <c r="F108">
-        <v>6848.7837130653252</v>
+        <v>7.5284216775458965</v>
       </c>
       <c r="G108">
-        <v>7.5284216775458965</v>
+        <v>1111.334351</v>
       </c>
       <c r="H108">
-        <v>1111.334351</v>
+        <v>4.234896</v>
       </c>
       <c r="I108">
-        <v>4.234896</v>
+        <v>1.401508</v>
       </c>
       <c r="J108">
-        <v>1.401508</v>
+        <v>49.204599999999999</v>
       </c>
       <c r="K108">
-        <v>49.204599999999999</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>2.1604969999999999</v>
       </c>
       <c r="M108">
-        <v>2.1604969999999999</v>
+        <v>8.0946719999999992</v>
       </c>
       <c r="N108">
-        <v>8.0946719999999992</v>
+        <v>323.46280000000002</v>
       </c>
       <c r="O108">
-        <v>323.46280000000002</v>
-      </c>
-      <c r="P108">
         <v>1.0565040000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>77</v>
       </c>
-      <c r="B109">
-        <v>7</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B109" t="s">
         <v>106</v>
       </c>
+      <c r="C109">
+        <v>77014</v>
+      </c>
       <c r="D109">
-        <v>77014</v>
+        <v>451</v>
       </c>
       <c r="E109">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F109">
-        <v>450</v>
+        <v>2</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>1023.773315</v>
       </c>
       <c r="H109">
-        <v>1023.773315</v>
+        <v>0.53333299999999995</v>
       </c>
       <c r="I109">
-        <v>0.53333299999999995</v>
+        <v>0.11712</v>
       </c>
       <c r="J109">
-        <v>0.11712</v>
+        <v>49.78</v>
       </c>
       <c r="K109">
-        <v>49.78</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="M109">
-        <v>4.21</v>
+        <v>11.51</v>
       </c>
       <c r="N109">
-        <v>11.51</v>
+        <v>536.49120000000005</v>
       </c>
       <c r="O109">
-        <v>536.49120000000005</v>
-      </c>
-      <c r="P109">
         <v>1.429257</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>77</v>
       </c>
-      <c r="B110">
-        <v>7</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="B110" t="s">
         <v>107</v>
       </c>
+      <c r="C110">
+        <v>69005</v>
+      </c>
       <c r="D110">
-        <v>69005</v>
+        <v>451</v>
       </c>
       <c r="E110">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F110">
-        <v>450</v>
+        <v>2</v>
       </c>
       <c r="G110">
-        <v>2</v>
+        <v>1838.71</v>
       </c>
       <c r="H110">
-        <v>1838.71</v>
+        <v>13.37</v>
       </c>
       <c r="I110">
-        <v>13.37</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="J110">
-        <v>2.1120000000000001</v>
+        <v>71.52</v>
       </c>
       <c r="K110">
-        <v>71.52</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M110">
-        <v>3.4</v>
+        <v>9.34</v>
       </c>
       <c r="N110">
-        <v>9.34</v>
+        <v>776</v>
       </c>
       <c r="O110">
-        <v>776</v>
-      </c>
-      <c r="P110">
         <v>1.552257</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>77</v>
       </c>
-      <c r="B111">
-        <v>7</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="B111" t="s">
         <v>108</v>
       </c>
+      <c r="C111">
+        <v>80036</v>
+      </c>
       <c r="D111">
-        <v>80036</v>
+        <v>942.55692023243523</v>
       </c>
       <c r="E111">
-        <v>942.55692023243523</v>
+        <v>681.0770230540021</v>
       </c>
       <c r="F111">
-        <v>681.0770230540021</v>
+        <v>7.2333333333333334</v>
       </c>
       <c r="G111">
-        <v>7.2333333333333334</v>
+        <v>1133.329956</v>
       </c>
       <c r="H111">
-        <v>1133.329956</v>
+        <v>20.38</v>
       </c>
       <c r="I111">
-        <v>20.38</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J111">
-        <v>8.6999999999999993</v>
+        <v>0</v>
       </c>
       <c r="K111">
         <v>0</v>
@@ -6662,48 +6332,45 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>22.28</v>
       </c>
       <c r="N111">
-        <v>22.28</v>
+        <v>4439.55</v>
       </c>
       <c r="O111">
-        <v>4439.55</v>
-      </c>
-      <c r="P111">
         <v>1.587089</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>196</v>
       </c>
-      <c r="B112">
-        <v>8</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="B112" t="s">
         <v>109</v>
       </c>
+      <c r="C112">
+        <v>69066</v>
+      </c>
       <c r="D112">
-        <v>69066</v>
+        <v>249</v>
       </c>
       <c r="E112">
-        <v>249</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F112">
-        <v>799.0934543872396</v>
+        <v>1</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="H112">
-        <v>676</v>
+        <v>10</v>
       </c>
       <c r="I112">
-        <v>10</v>
+        <v>3.7628279999999998</v>
       </c>
       <c r="J112">
-        <v>3.7628279999999998</v>
+        <v>0</v>
       </c>
       <c r="K112">
         <v>0</v>
@@ -6712,351 +6379,330 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N112">
-        <v>18</v>
+        <v>49.339770000000001</v>
       </c>
       <c r="O112">
-        <v>49.339770000000001</v>
-      </c>
-      <c r="P112">
         <v>2.1117780000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>196</v>
       </c>
-      <c r="B113">
-        <v>8</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="B113" t="s">
         <v>110</v>
       </c>
+      <c r="C113">
+        <v>69069</v>
+      </c>
       <c r="D113">
-        <v>69069</v>
+        <v>205.00695976154995</v>
       </c>
       <c r="E113">
-        <v>205.00695976154995</v>
+        <v>539.4710810974143</v>
       </c>
       <c r="F113">
-        <v>539.4710810974143</v>
+        <v>2.4283582089552236</v>
       </c>
       <c r="G113">
-        <v>2.4283582089552236</v>
+        <v>909.24932860000001</v>
       </c>
       <c r="H113">
-        <v>909.24932860000001</v>
+        <v>14.69778</v>
       </c>
       <c r="I113">
-        <v>14.69778</v>
+        <v>4.373958</v>
       </c>
       <c r="J113">
-        <v>4.373958</v>
+        <v>7.6671490000000002</v>
       </c>
       <c r="K113">
-        <v>7.6671490000000002</v>
+        <v>0</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>13.82882</v>
       </c>
       <c r="N113">
-        <v>13.82882</v>
+        <v>1194.0550000000001</v>
       </c>
       <c r="O113">
-        <v>1194.0550000000001</v>
-      </c>
-      <c r="P113">
         <v>0.75075999999999998</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>196</v>
       </c>
-      <c r="B114">
-        <v>8</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="B114" t="s">
         <v>111</v>
       </c>
+      <c r="C114">
+        <v>82080</v>
+      </c>
       <c r="D114">
-        <v>82080</v>
+        <v>77</v>
       </c>
       <c r="E114">
-        <v>77</v>
+        <v>451.0581751901363</v>
       </c>
       <c r="F114">
-        <v>451.0581751901363</v>
+        <v>3.0946988062765213</v>
       </c>
       <c r="G114">
-        <v>3.0946988062765213</v>
+        <v>1219.1247559999999</v>
       </c>
       <c r="H114">
-        <v>1219.1247559999999</v>
+        <v>22.928319999999999</v>
       </c>
       <c r="I114">
-        <v>22.928319999999999</v>
+        <v>5.2157229999999997</v>
       </c>
       <c r="J114">
-        <v>5.2157229999999997</v>
+        <v>0.86331100000000005</v>
       </c>
       <c r="K114">
-        <v>0.86331100000000005</v>
+        <v>0</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>20.947099999999999</v>
       </c>
       <c r="N114">
-        <v>20.947099999999999</v>
+        <v>1533.06</v>
       </c>
       <c r="O114">
-        <v>1533.06</v>
-      </c>
-      <c r="P114">
         <v>1.2687349999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>196</v>
       </c>
-      <c r="B115">
-        <v>8</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B115" t="s">
         <v>112</v>
       </c>
+      <c r="C115">
+        <v>79010</v>
+      </c>
       <c r="D115">
-        <v>79010</v>
+        <v>558.33333333333337</v>
       </c>
       <c r="E115">
-        <v>558.33333333333337</v>
+        <v>1254.7498947363872</v>
       </c>
       <c r="F115">
-        <v>1254.7498947363872</v>
+        <v>3.2495477253553973</v>
       </c>
       <c r="G115">
-        <v>3.2495477253553973</v>
+        <v>506.89205930000003</v>
       </c>
       <c r="H115">
-        <v>506.89205930000003</v>
+        <v>5.6963330000000001</v>
       </c>
       <c r="I115">
-        <v>5.6963330000000001</v>
+        <v>1.401667</v>
       </c>
       <c r="J115">
-        <v>1.401667</v>
+        <v>2.315528</v>
       </c>
       <c r="K115">
-        <v>2.315528</v>
+        <v>0</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>15.10375</v>
       </c>
       <c r="N115">
-        <v>15.10375</v>
+        <v>1201.9860000000001</v>
       </c>
       <c r="O115">
-        <v>1201.9860000000001</v>
-      </c>
-      <c r="P115">
         <v>2.0802520000000002</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>196</v>
       </c>
-      <c r="B116">
-        <v>8</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" t="s">
         <v>113</v>
       </c>
+      <c r="C116">
+        <v>69013</v>
+      </c>
       <c r="D116">
-        <v>69013</v>
+        <v>461</v>
       </c>
       <c r="E116">
-        <v>461</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F116">
-        <v>799.0934543872396</v>
+        <v>1.5</v>
       </c>
       <c r="G116">
-        <v>1.5</v>
+        <v>1017.643677</v>
       </c>
       <c r="H116">
-        <v>1017.643677</v>
+        <v>15.561</v>
       </c>
       <c r="I116">
-        <v>15.561</v>
+        <v>3.4887570000000001</v>
       </c>
       <c r="J116">
-        <v>3.4887570000000001</v>
+        <v>13.949579999999999</v>
       </c>
       <c r="K116">
-        <v>13.949579999999999</v>
+        <v>0</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>12.043749999999999</v>
       </c>
       <c r="N116">
-        <v>12.043749999999999</v>
+        <v>710.63729999999998</v>
       </c>
       <c r="O116">
-        <v>710.63729999999998</v>
-      </c>
-      <c r="P116">
         <v>1.2714589999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>196</v>
       </c>
-      <c r="B117">
-        <v>8</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" t="s">
         <v>114</v>
       </c>
+      <c r="C117">
+        <v>70006</v>
+      </c>
       <c r="D117">
-        <v>70006</v>
+        <v>167.70491803278688</v>
       </c>
       <c r="E117">
-        <v>167.70491803278688</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F117">
-        <v>799.0934543872396</v>
+        <v>1.5</v>
       </c>
       <c r="G117">
-        <v>1.5</v>
+        <v>1113.5</v>
       </c>
       <c r="H117">
-        <v>1113.5</v>
+        <v>17</v>
       </c>
       <c r="I117">
-        <v>17</v>
+        <v>3.7153049999999999</v>
       </c>
       <c r="J117">
-        <v>3.7153049999999999</v>
+        <v>18</v>
       </c>
       <c r="K117">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N117">
-        <v>10.5</v>
+        <v>536.88149999999996</v>
       </c>
       <c r="O117">
-        <v>536.88149999999996</v>
-      </c>
-      <c r="P117">
         <v>0.85813899999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>196</v>
       </c>
-      <c r="B118">
-        <v>8</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" t="s">
         <v>115</v>
       </c>
+      <c r="C118">
+        <v>69016</v>
+      </c>
       <c r="D118">
-        <v>69016</v>
+        <v>337.41888888888889</v>
       </c>
       <c r="E118">
-        <v>337.41888888888889</v>
+        <v>416.07420888875833</v>
       </c>
       <c r="F118">
-        <v>416.07420888875833</v>
+        <v>2.158507462686567</v>
       </c>
       <c r="G118">
-        <v>2.158507462686567</v>
+        <v>88.668334959999996</v>
       </c>
       <c r="H118">
-        <v>88.668334959999996</v>
+        <v>1E-4</v>
       </c>
       <c r="I118">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>0</v>
+        <v>5.284567</v>
       </c>
       <c r="K118">
-        <v>5.284567</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>0.130333</v>
       </c>
       <c r="M118">
-        <v>0.130333</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.7823329999999999</v>
       </c>
       <c r="O118">
-        <v>1.7823329999999999</v>
-      </c>
-      <c r="P118">
         <v>0.69677199999999995</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>196</v>
       </c>
-      <c r="B119">
-        <v>8</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" t="s">
         <v>116</v>
       </c>
+      <c r="C119">
+        <v>70080</v>
+      </c>
       <c r="D119">
-        <v>70080</v>
+        <v>209.15</v>
       </c>
       <c r="E119">
-        <v>209.15</v>
+        <v>2781.396945988402</v>
       </c>
       <c r="F119">
-        <v>2781.396945988402</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="G119">
-        <v>1.2333333333333334</v>
+        <v>165.46665949999999</v>
       </c>
       <c r="H119">
-        <v>165.46665949999999</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>0</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>9.7333339999999993</v>
       </c>
       <c r="K119">
-        <v>9.7333339999999993</v>
+        <v>0</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -7065,98 +6711,92 @@
         <v>0</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>8.1178609999999995</v>
       </c>
       <c r="O119">
-        <v>8.1178609999999995</v>
-      </c>
-      <c r="P119">
         <v>0.25438899999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>196</v>
       </c>
-      <c r="B120">
-        <v>8</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" t="s">
         <v>117</v>
       </c>
+      <c r="C120">
+        <v>70001</v>
+      </c>
       <c r="D120">
-        <v>70001</v>
+        <v>110</v>
       </c>
       <c r="E120">
-        <v>110</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F120">
-        <v>799.0934543872396</v>
+        <v>0.5</v>
       </c>
       <c r="G120">
-        <v>0.5</v>
+        <v>247.93600459999999</v>
       </c>
       <c r="H120">
-        <v>247.93600459999999</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>0</v>
       </c>
       <c r="J120">
-        <v>0</v>
+        <v>14.708</v>
       </c>
       <c r="K120">
-        <v>14.708</v>
+        <v>5</v>
       </c>
       <c r="L120">
-        <v>5</v>
+        <v>0.23333300000000001</v>
       </c>
       <c r="M120">
-        <v>0.23333300000000001</v>
+        <v>0</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>9.5833329999999997</v>
       </c>
       <c r="O120">
-        <v>9.5833329999999997</v>
-      </c>
-      <c r="P120">
         <v>0.60425200000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>196</v>
       </c>
-      <c r="B121">
-        <v>8</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="B121" t="s">
         <v>118</v>
       </c>
+      <c r="C121">
+        <v>70088</v>
+      </c>
       <c r="D121">
-        <v>70088</v>
+        <v>209.15</v>
       </c>
       <c r="E121">
-        <v>209.15</v>
+        <v>465.48330790858756</v>
       </c>
       <c r="F121">
-        <v>465.48330790858756</v>
+        <v>1.2</v>
       </c>
       <c r="G121">
-        <v>1.2</v>
+        <v>10.07066631</v>
       </c>
       <c r="H121">
-        <v>10.07066631</v>
+        <v>1.7333000000000001E-2</v>
       </c>
       <c r="I121">
-        <v>1.7333000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>0.55466700000000002</v>
       </c>
       <c r="K121">
-        <v>0.55466700000000002</v>
+        <v>0</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -7165,95 +6805,89 @@
         <v>0</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>0.21252799999999999</v>
       </c>
       <c r="O121">
-        <v>0.21252799999999999</v>
-      </c>
-      <c r="P121">
         <v>2.0480749999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>119</v>
       </c>
-      <c r="B122">
-        <v>9</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" t="s">
         <v>120</v>
       </c>
+      <c r="C122">
+        <v>82157</v>
+      </c>
       <c r="D122">
-        <v>82157</v>
+        <v>249</v>
       </c>
       <c r="E122">
-        <v>249</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F122">
-        <v>799.0934543872396</v>
+        <v>1</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>1.7000000479999999</v>
       </c>
       <c r="H122">
-        <v>1.7000000479999999</v>
+        <v>0</v>
       </c>
       <c r="I122">
         <v>0</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="K122">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N122">
-        <v>0.1</v>
+        <v>13.9</v>
       </c>
       <c r="O122">
-        <v>13.9</v>
-      </c>
-      <c r="P122">
         <v>0.23494200000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>119</v>
       </c>
-      <c r="B123">
-        <v>9</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="B123" t="s">
         <v>121</v>
       </c>
+      <c r="C123">
+        <v>82063</v>
+      </c>
       <c r="D123">
-        <v>82063</v>
+        <v>209.15</v>
       </c>
       <c r="E123">
-        <v>209.15</v>
+        <v>1623.4401269484947</v>
       </c>
       <c r="F123">
-        <v>1623.4401269484947</v>
+        <v>1.2</v>
       </c>
       <c r="G123">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J123">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K123">
         <v>0</v>
@@ -7265,189 +6899,177 @@
         <v>0</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O123">
-        <v>3</v>
-      </c>
-      <c r="P123">
         <v>1.2585000000000001E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>122</v>
       </c>
-      <c r="B124">
-        <v>10</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" t="s">
         <v>123</v>
       </c>
+      <c r="C124">
+        <v>83003</v>
+      </c>
       <c r="D124">
-        <v>83003</v>
+        <v>335.30210772833726</v>
       </c>
       <c r="E124">
-        <v>335.30210772833726</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F124">
-        <v>799.0934543872396</v>
+        <v>1.5</v>
       </c>
       <c r="G124">
-        <v>1.5</v>
+        <v>4.7590999600000004</v>
       </c>
       <c r="H124">
-        <v>4.7590999600000004</v>
+        <v>0</v>
       </c>
       <c r="I124">
         <v>0</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K124">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="M124">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>0.77777799999999997</v>
       </c>
       <c r="O124">
-        <v>0.77777799999999997</v>
-      </c>
-      <c r="P124">
         <v>0.79635699999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>122</v>
       </c>
-      <c r="B125">
-        <v>10</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B125" t="s">
         <v>124</v>
       </c>
+      <c r="C125">
+        <v>83035</v>
+      </c>
       <c r="D125">
-        <v>83035</v>
+        <v>349.4</v>
       </c>
       <c r="E125">
-        <v>349.4</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F125">
-        <v>799.0934543872396</v>
+        <v>1.35</v>
       </c>
       <c r="G125">
-        <v>1.35</v>
+        <v>34.024733329999997</v>
       </c>
       <c r="H125">
-        <v>34.024733329999997</v>
+        <v>5.5467000000000002E-2</v>
       </c>
       <c r="I125">
-        <v>5.5467000000000002E-2</v>
+        <v>5.5469999999999998E-3</v>
       </c>
       <c r="J125">
-        <v>5.5469999999999998E-3</v>
+        <v>1.3437330000000001</v>
       </c>
       <c r="K125">
-        <v>1.3437330000000001</v>
+        <v>0</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="N125">
-        <v>0.53700000000000003</v>
+        <v>0.82186700000000001</v>
       </c>
       <c r="O125">
-        <v>0.82186700000000001</v>
-      </c>
-      <c r="P125">
         <v>1.518607</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>122</v>
       </c>
-      <c r="B126">
-        <v>10</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B126" t="s">
         <v>125</v>
       </c>
+      <c r="C126">
+        <v>83001</v>
+      </c>
       <c r="D126">
-        <v>83001</v>
+        <v>337.41888888888889</v>
       </c>
       <c r="E126">
-        <v>337.41888888888889</v>
+        <v>416.07420888875833</v>
       </c>
       <c r="F126">
-        <v>416.07420888875833</v>
+        <v>2.158507462686567</v>
       </c>
       <c r="G126">
-        <v>2.158507462686567</v>
+        <v>170.6999969</v>
       </c>
       <c r="H126">
-        <v>170.6999969</v>
+        <v>0</v>
       </c>
       <c r="I126">
         <v>0</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>3.3374999999999999</v>
       </c>
       <c r="K126">
-        <v>3.3374999999999999</v>
+        <v>0</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="N126">
-        <v>0.5625</v>
+        <v>4.2303329999999999</v>
       </c>
       <c r="O126">
-        <v>4.2303329999999999</v>
-      </c>
-      <c r="P126">
         <v>0.67746099999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>122</v>
       </c>
-      <c r="B127">
-        <v>10</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="B127" t="s">
         <v>126</v>
       </c>
+      <c r="C127">
+        <v>83024</v>
+      </c>
       <c r="D127">
-        <v>83024</v>
+        <v>1730.4937285223366</v>
       </c>
       <c r="E127">
-        <v>1730.4937285223366</v>
+        <v>1247.109290423776</v>
       </c>
       <c r="F127">
-        <v>1247.109290423776</v>
+        <v>5</v>
       </c>
       <c r="G127">
-        <v>5</v>
+        <v>901.90002440000001</v>
       </c>
       <c r="H127">
-        <v>901.90002440000001</v>
+        <v>0</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -7465,195 +7087,183 @@
         <v>0</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>3.145667</v>
       </c>
       <c r="O127">
-        <v>3.145667</v>
-      </c>
-      <c r="P127">
         <v>1.0057100000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>119</v>
       </c>
-      <c r="B128">
-        <v>11</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="B128" t="s">
         <v>127</v>
       </c>
+      <c r="C128">
+        <v>82074</v>
+      </c>
       <c r="D128">
-        <v>82074</v>
+        <v>327.12704918032784</v>
       </c>
       <c r="E128">
-        <v>327.12704918032784</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F128">
-        <v>799.0934543872396</v>
+        <v>3.0946988062765213</v>
       </c>
       <c r="G128">
-        <v>3.0946988062765213</v>
+        <v>381.91558839999999</v>
       </c>
       <c r="H128">
-        <v>381.91558839999999</v>
+        <v>1E-4</v>
       </c>
       <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>3.4051079999999998</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
         <v>1E-4</v>
       </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>3.4051079999999998</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
       <c r="M128">
-        <v>1E-4</v>
+        <v>7.7292E-2</v>
       </c>
       <c r="N128">
-        <v>7.7292E-2</v>
+        <v>2.578182</v>
       </c>
       <c r="O128">
-        <v>2.578182</v>
-      </c>
-      <c r="P128">
         <v>1.8200350000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>119</v>
       </c>
-      <c r="B129">
-        <v>11</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="B129" t="s">
         <v>128</v>
       </c>
+      <c r="C129">
+        <v>82035</v>
+      </c>
       <c r="D129">
-        <v>82035</v>
+        <v>350.03447540983609</v>
       </c>
       <c r="E129">
-        <v>350.03447540983609</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F129">
-        <v>799.0934543872396</v>
+        <v>1.45</v>
       </c>
       <c r="G129">
-        <v>1.45</v>
+        <v>170.6999969</v>
       </c>
       <c r="H129">
-        <v>170.6999969</v>
+        <v>0</v>
       </c>
       <c r="I129">
         <v>0</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>3.3374999999999999</v>
       </c>
       <c r="K129">
-        <v>3.3374999999999999</v>
+        <v>0</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="N129">
-        <v>0.5625</v>
+        <v>4.2303329999999999</v>
       </c>
       <c r="O129">
-        <v>4.2303329999999999</v>
-      </c>
-      <c r="P129">
         <v>1.1148229999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>119</v>
       </c>
-      <c r="B130">
-        <v>11</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="B130" t="s">
         <v>129</v>
       </c>
+      <c r="C130">
+        <v>82062</v>
+      </c>
       <c r="D130">
-        <v>82062</v>
+        <v>107</v>
       </c>
       <c r="E130">
-        <v>107</v>
+        <v>799.0934543872396</v>
       </c>
       <c r="F130">
-        <v>799.0934543872396</v>
+        <v>1.25</v>
       </c>
       <c r="G130">
-        <v>1.25</v>
+        <v>170.6999969</v>
       </c>
       <c r="H130">
-        <v>170.6999969</v>
+        <v>0</v>
       </c>
       <c r="I130">
         <v>0</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>3.3374999999999999</v>
       </c>
       <c r="K130">
-        <v>3.3374999999999999</v>
+        <v>0</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="N130">
-        <v>0.5625</v>
+        <v>4.2303329999999999</v>
       </c>
       <c r="O130">
-        <v>4.2303329999999999</v>
-      </c>
-      <c r="P130">
         <v>1.1148229999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
-      <c r="B131">
-        <v>12</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="B131" t="s">
         <v>130</v>
       </c>
+      <c r="C131">
+        <v>64003</v>
+      </c>
       <c r="D131">
-        <v>64003</v>
+        <v>477.7</v>
       </c>
       <c r="E131">
-        <v>477.7</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F131">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G131">
-        <v>57.5</v>
+        <v>3700</v>
       </c>
       <c r="H131">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="I131">
-        <v>100</v>
+        <v>14.9</v>
       </c>
       <c r="J131">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -7665,45 +7275,42 @@
         <v>0</v>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131">
-        <v>2</v>
-      </c>
-      <c r="P131">
         <v>2.8359830000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>145</v>
       </c>
-      <c r="B132">
-        <v>12</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B132" t="s">
         <v>131</v>
       </c>
+      <c r="C132">
+        <v>64008</v>
+      </c>
       <c r="D132">
-        <v>64008</v>
+        <v>477.7</v>
       </c>
       <c r="E132">
-        <v>477.7</v>
+        <v>1518.8519501739984</v>
       </c>
       <c r="F132">
-        <v>1518.8519501739984</v>
+        <v>57.5</v>
       </c>
       <c r="G132">
-        <v>57.5</v>
+        <v>3700</v>
       </c>
       <c r="H132">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="I132">
-        <v>100</v>
+        <v>15.2</v>
       </c>
       <c r="J132">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7718,109 +7325,100 @@
         <v>0</v>
       </c>
       <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
         <v>0.44218000000000002</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>145</v>
       </c>
-      <c r="B133">
-        <v>12</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="B133" t="s">
         <v>132</v>
       </c>
+      <c r="C133">
+        <v>64006</v>
+      </c>
       <c r="D133">
-        <v>64006</v>
+        <v>337.41888888888889</v>
       </c>
       <c r="E133">
-        <v>337.41888888888889</v>
+        <v>416.07420888875833</v>
       </c>
       <c r="F133">
-        <v>416.07420888875833</v>
+        <v>1.9417910447761193</v>
       </c>
       <c r="G133">
-        <v>1.9417910447761193</v>
+        <v>287.63009640000001</v>
       </c>
       <c r="H133">
-        <v>287.63009640000001</v>
+        <v>4.6561880000000002</v>
       </c>
       <c r="I133">
-        <v>4.6561880000000002</v>
+        <v>0.73027399999999998</v>
       </c>
       <c r="J133">
-        <v>0.73027399999999998</v>
+        <v>6.8780799999999997</v>
       </c>
       <c r="K133">
-        <v>6.8780799999999997</v>
+        <v>0</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>1.5989469999999999</v>
       </c>
       <c r="M133">
-        <v>1.5989469999999999</v>
+        <v>0.75378100000000003</v>
       </c>
       <c r="N133">
-        <v>0.75378100000000003</v>
+        <v>129.69329999999999</v>
       </c>
       <c r="O133">
-        <v>129.69329999999999</v>
-      </c>
-      <c r="P133">
         <v>1.706742</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>145</v>
       </c>
-      <c r="B134">
-        <v>12</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" t="s">
         <v>133</v>
       </c>
+      <c r="C134">
+        <v>63007</v>
+      </c>
       <c r="D134">
-        <v>63007</v>
+        <v>751.57998140949815</v>
       </c>
       <c r="E134">
-        <v>751.57998140949815</v>
+        <v>80.09236899680279</v>
       </c>
       <c r="F134">
-        <v>80.09236899680279</v>
+        <v>0.8</v>
       </c>
       <c r="G134">
-        <v>0.8</v>
+        <v>185.34455869999999</v>
       </c>
       <c r="H134">
-        <v>185.34455869999999</v>
+        <v>3.537407</v>
       </c>
       <c r="I134">
-        <v>3.537407</v>
+        <v>0.57549600000000001</v>
       </c>
       <c r="J134">
-        <v>0.57549600000000001</v>
+        <v>2.6027140000000002</v>
       </c>
       <c r="K134">
-        <v>2.6027140000000002</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>1.7056800000000001</v>
       </c>
       <c r="M134">
-        <v>1.7056800000000001</v>
+        <v>1.503852</v>
       </c>
       <c r="N134">
-        <v>1.503852</v>
+        <v>59.898040000000002</v>
       </c>
       <c r="O134">
-        <v>59.898040000000002</v>
-      </c>
-      <c r="P134">
         <v>1.48376</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbrac\OneDrive\Documentos\Nutrição\Produtos\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471646C9-E569-42D2-B7CB-331785D43CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE7CB8A-6F10-4F19-B623-47F17BA8A48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{3BD6BFFB-CC8B-41FE-8C98-25F5632F7E13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3BD6BFFB-CC8B-41FE-8C98-25F5632F7E13}"/>
   </bookViews>
   <sheets>
     <sheet name="food_data" sheetId="1" r:id="rId1"/>
@@ -1203,7 +1203,7 @@
         <v>79.070329999999998</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="L2">
         <v>1.6830000000000001</v>
@@ -1250,7 +1250,7 @@
         <v>76.361919999999998</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.31408999999999998</v>
       </c>
       <c r="L3">
         <v>3.8995829999999998</v>
@@ -1297,7 +1297,7 @@
         <v>28.55575</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>9.7439999999999999E-2</v>
       </c>
       <c r="L4">
         <v>3.9180000000000001</v>
@@ -1344,7 +1344,7 @@
         <v>20.671769999999999</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="L5">
         <v>6.218</v>
@@ -1391,7 +1391,7 @@
         <v>59.15</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="L6">
         <v>20.8</v>
@@ -1438,7 +1438,7 @@
         <v>62.929160000000003</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L7">
         <v>24.00667</v>
@@ -1485,7 +1485,7 @@
         <v>57.45</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>3.2259929999999999</v>
       </c>
       <c r="L8">
         <v>11</v>
@@ -1532,7 +1532,7 @@
         <v>21.571449999999999</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3.0393E-2</v>
       </c>
       <c r="L9">
         <v>1.931667</v>
@@ -1579,7 +1579,7 @@
         <v>32.589860000000002</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>4.5467E-2</v>
       </c>
       <c r="L10">
         <v>2.085556</v>
@@ -1626,7 +1626,7 @@
         <v>16.53565</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L11">
         <v>1.32</v>
@@ -1673,7 +1673,7 @@
         <v>11.11101</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1.4E-2</v>
       </c>
       <c r="L12">
         <v>3.3733330000000001</v>
@@ -1720,7 +1720,7 @@
         <v>7.5465070000000001</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="L13">
         <v>2.983333</v>
@@ -1767,7 +1767,7 @@
         <v>64.5</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1.558729</v>
       </c>
       <c r="L14">
         <v>9.5</v>
@@ -1814,7 +1814,7 @@
         <v>75.52628</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>0.30810999999999999</v>
       </c>
       <c r="L15">
         <v>2.5833330000000001</v>
@@ -1908,7 +1908,7 @@
         <v>75.52628</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>0.30810999999999999</v>
       </c>
       <c r="L17">
         <v>2.5833330000000001</v>
@@ -1955,7 +1955,7 @@
         <v>76.56</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>0.490566</v>
       </c>
       <c r="L18">
         <v>6.25</v>
@@ -2002,7 +2002,7 @@
         <v>51.3</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1.959579</v>
       </c>
       <c r="L19">
         <v>3.25</v>
@@ -2049,7 +2049,7 @@
         <v>51.3</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1.959579</v>
       </c>
       <c r="L20">
         <v>3.25</v>
@@ -2096,7 +2096,7 @@
         <v>76.622540000000001</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>0.53533299999999995</v>
       </c>
       <c r="L21">
         <v>2.2966669999999998</v>
@@ -2143,7 +2143,7 @@
         <v>62.05</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="L22">
         <v>7.83</v>
@@ -2190,7 +2190,7 @@
         <v>62.431649999999998</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2.4739559999999998</v>
       </c>
       <c r="L23">
         <v>5.61</v>
@@ -2237,7 +2237,7 @@
         <v>40.98639</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>0.273675</v>
       </c>
       <c r="L24">
         <v>8.4614010000000004</v>
@@ -2284,7 +2284,7 @@
         <v>87.071849999999998</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>0.29333300000000001</v>
       </c>
       <c r="L25">
         <v>2.2479170000000002</v>
@@ -2331,7 +2331,7 @@
         <v>7.6571210000000001</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1.0106329999999999</v>
       </c>
       <c r="L26">
         <v>5.8883330000000003</v>
@@ -2378,7 +2378,7 @@
         <v>30.19</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>7.7830000000000004</v>
       </c>
       <c r="L27">
         <v>3.3</v>
@@ -2425,7 +2425,7 @@
         <v>1.791256</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L28">
         <v>1.8722220000000001</v>
@@ -2472,7 +2472,7 @@
         <v>4.3334780000000004</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L29">
         <v>3.12</v>
@@ -2519,7 +2519,7 @@
         <v>4.4199520000000003</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="L30">
         <v>1.923333</v>
@@ -2566,7 +2566,7 @@
         <v>5.840363</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L31">
         <v>2.6475</v>
@@ -2613,7 +2613,7 @@
         <v>3.7110150000000002</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>3.1E-2</v>
       </c>
       <c r="L32">
         <v>1.2816669999999999</v>
@@ -2660,7 +2660,7 @@
         <v>5.0293900000000002</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L33">
         <v>2.0160670000000001</v>
@@ -2707,7 +2707,7 @@
         <v>2.2345890000000002</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>3.0273000000000001E-2</v>
       </c>
       <c r="L34">
         <v>1.036667</v>
@@ -2754,7 +2754,7 @@
         <v>4.1736959999999996</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1.29E-2</v>
       </c>
       <c r="L35">
         <v>1.4</v>
@@ -2801,7 +2801,7 @@
         <v>5.2459210000000001</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>4.9174000000000002E-2</v>
       </c>
       <c r="L36">
         <v>1.674167</v>
@@ -2848,7 +2848,7 @@
         <v>3.817475</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>2.4E-2</v>
       </c>
       <c r="L37">
         <v>1.5972219999999999</v>
@@ -2895,7 +2895,7 @@
         <v>9.2065940000000008</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>5.4600000000000003E-2</v>
       </c>
       <c r="L38">
         <v>2.0433330000000001</v>
@@ -2942,7 +2942,7 @@
         <v>25.758600000000001</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>3.56E-2</v>
       </c>
       <c r="L39">
         <v>3.1944439999999998</v>
@@ -2989,7 +2989,7 @@
         <v>1.6955070000000001</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>0.21333299999999999</v>
       </c>
       <c r="L40">
         <v>1.826667</v>
@@ -3036,7 +3036,7 @@
         <v>25.933440000000001</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>9.3299999999999994E-2</v>
       </c>
       <c r="L41">
         <v>1.9466669999999999</v>
@@ -3224,7 +3224,7 @@
         <v>11.61347</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="L45">
         <v>1.1166670000000001</v>
@@ -3271,7 +3271,7 @@
         <v>15.65189</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L46">
         <v>2.0705</v>
@@ -3318,7 +3318,7 @@
         <v>10.71691</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="L47">
         <v>1.828667</v>
@@ -3365,7 +3365,7 @@
         <v>15.958959999999999</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L48">
         <v>2.1404999999999998</v>
@@ -3459,7 +3459,7 @@
         <v>5.7</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L50">
         <v>1.22</v>
@@ -3506,7 +3506,7 @@
         <v>13.706490000000001</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="L51">
         <v>0.92683300000000002</v>
@@ -3600,7 +3600,7 @@
         <v>26.6</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="L53">
         <v>0.93333299999999997</v>
@@ -3647,7 +3647,7 @@
         <v>97</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="L54">
         <v>2.4</v>
@@ -3694,7 +3694,7 @@
         <v>66.813789999999997</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>14.367520000000001</v>
       </c>
       <c r="L55">
         <v>1.786897</v>
@@ -3835,7 +3835,7 @@
         <v>72.555999999999997</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>0.35220000000000001</v>
       </c>
       <c r="L58">
         <v>5.3159999999999998</v>
@@ -3882,7 +3882,7 @@
         <v>16.86749</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>9.74</v>
       </c>
       <c r="L59">
         <v>8.9944450000000007</v>
@@ -3929,7 +3929,7 @@
         <v>98.323599999999999</v>
       </c>
       <c r="K60">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>58.806429999999999</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1.374814</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>40.306379999999997</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>9.1783800000000006</v>
       </c>
       <c r="L63">
         <v>1.888957</v>
@@ -4164,7 +4164,7 @@
         <v>43.91133</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1.3383000000000001E-2</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -4211,7 +4211,7 @@
         <v>9.01</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>0.11681900000000001</v>
       </c>
       <c r="L66">
         <v>3.64</v>
@@ -4352,7 +4352,7 @@
         <v>8.1110000000000002E-3</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>1.3833329999999999</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0.46</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>1.501949</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>1.501949</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0.46</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>1.501949</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>0.80778700000000003</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -4775,7 +4775,7 @@
         <v>8.0850000000000009</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>0.182033</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -4822,7 +4822,7 @@
         <v>1.333E-3</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>0.79250299999999996</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>20.403230000000001</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>0.30794700000000003</v>
       </c>
       <c r="L81">
         <v>4.7522219999999997</v>
@@ -4963,7 +4963,7 @@
         <v>63.378329999999998</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>1.6020179999999999</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>1.4619439999999999</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>1.105985</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>7.85</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="L84">
         <v>0.9</v>
@@ -5104,7 +5104,7 @@
         <v>0.80679599999999996</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>3.1555550000000001</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -5151,7 +5151,7 @@
         <v>0.03</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>2.1327780000000001</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>2.6423589999999999</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -5245,7 +5245,7 @@
         <v>38.950000000000003</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>16.0107</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>56.996670000000002</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>4.154763</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>11.82</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>10.9215</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L91">
         <v>0.23333300000000001</v>
@@ -5433,7 +5433,7 @@
         <v>0.51776800000000001</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>44.933329999999998</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>19.233329999999999</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>4.1181660000000004</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>16.173739999999999</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>4.1181660000000004</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -5621,7 +5621,7 @@
         <v>13.9</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>1.2171510000000001</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>4.154763</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>11.82</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>6.51</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>1.149076</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -5762,7 +5762,7 @@
         <v>7.0369770000000003</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>0.26473099999999999</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>1.6</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>8.0069110000000006</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -5903,7 +5903,7 @@
         <v>5.9160000000000004</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>2.0128560000000002</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>61.635480000000001</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="L103">
         <v>2.608889</v>
@@ -5997,7 +5997,7 @@
         <v>69.648110000000003</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L104">
         <v>3.17625</v>
@@ -6044,7 +6044,7 @@
         <v>76.278049999999993</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L105">
         <v>2.7366670000000002</v>
@@ -6091,7 +6091,7 @@
         <v>54.416670000000003</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>5.9815969999999998</v>
       </c>
       <c r="L106">
         <v>8.3333000000000004E-2</v>
@@ -6138,7 +6138,7 @@
         <v>16.73</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="L107">
         <v>0.51</v>
@@ -6185,7 +6185,7 @@
         <v>49.204599999999999</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>1.401508</v>
       </c>
       <c r="L108">
         <v>2.1604969999999999</v>
@@ -6232,7 +6232,7 @@
         <v>49.78</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>0.11712</v>
       </c>
       <c r="L109">
         <v>4.21</v>
@@ -6279,7 +6279,7 @@
         <v>71.52</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="L110">
         <v>3.4</v>
@@ -6326,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>3.7628279999999998</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>7.6671490000000002</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>4.373958</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -6467,7 +6467,7 @@
         <v>0.86331100000000005</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>5.2157229999999997</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>2.315528</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>1.401667</v>
       </c>
       <c r="L115">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>13.949579999999999</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>3.4887570000000001</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         <v>18</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>3.7153049999999999</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>14.708</v>
       </c>
       <c r="K120">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L120">
         <v>0.23333300000000001</v>
@@ -6890,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -6984,10 +6984,10 @@
         <v>1.3437330000000001</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>5.5469999999999998E-3</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M125">
         <v>0.53700000000000003</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="L132">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         <v>6.8780799999999997</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>0.73027399999999998</v>
       </c>
       <c r="L133">
         <v>1.5989469999999999</v>
@@ -7407,7 +7407,7 @@
         <v>2.6027140000000002</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>0.57549600000000001</v>
       </c>
       <c r="L134">
         <v>1.7056800000000001</v>
